--- a/AssessmentSchedule_2627_v2.xlsx
+++ b/AssessmentSchedule_2627_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cf-my.sharepoint.com/personal/northce_cardiff_ac_uk/Documents/Documents/Cardiff/DUGS/Assessments/Schedule Modelling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="138" documentId="8_{0C641013-E594-4AA6-B777-C2C249EA34A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D36459A6-560D-4828-AB55-DDC0D9F28339}"/>
+  <xr:revisionPtr revIDLastSave="139" documentId="8_{0C641013-E594-4AA6-B777-C2C249EA34A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{258D2691-5756-4211-A58E-D3673EA5C431}"/>
   <bookViews>
-    <workbookView xWindow="28702" yWindow="-98" windowWidth="26115" windowHeight="15675" activeTab="2" xr2:uid="{A20BCC1C-F123-4C76-9181-B345A7D760BE}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="26116" windowHeight="15675" activeTab="2" xr2:uid="{A20BCC1C-F123-4C76-9181-B345A7D760BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Assessments" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId5"/>
+    <pivotCache cacheId="9" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1409,7 +1409,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1560,27 +1560,15 @@
     <xf numFmtId="2" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="128">
+  <dxfs count="117">
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1607,130 +1595,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1847,310 +1712,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -4026,6 +3587,329 @@
         <bottom/>
       </border>
     </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -9426,7 +9310,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3F344565-A902-475D-ACD8-7DA2FB255CBD}" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3F344565-A902-475D-ACD8-7DA2FB255CBD}" name="PivotTable1" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:B70" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
   <pivotFields count="34">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -9875,54 +9759,54 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FA69A777-C149-48BD-B248-35F32F0AC920}" name="Table1" displayName="Table1" ref="A1:AL188" totalsRowShown="0" headerRowDxfId="127" dataDxfId="125" headerRowBorderDxfId="126" tableBorderDxfId="124" totalsRowBorderDxfId="123">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FA69A777-C149-48BD-B248-35F32F0AC920}" name="Table1" displayName="Table1" ref="A1:AL188" totalsRowShown="0" headerRowDxfId="94" dataDxfId="92" headerRowBorderDxfId="93" tableBorderDxfId="91" totalsRowBorderDxfId="90">
   <autoFilter ref="A1:AL188" xr:uid="{FA69A777-C149-48BD-B248-35F32F0AC920}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AI159">
     <sortCondition ref="A1:A159"/>
   </sortState>
   <tableColumns count="38">
-    <tableColumn id="1" xr3:uid="{7078548A-F011-4851-AB36-1F04238FA2FE}" name="Module Code" dataDxfId="122"/>
-    <tableColumn id="2" xr3:uid="{D2290F36-B8B3-427A-AEFE-45FD22901411}" name="Module Title" dataDxfId="121"/>
-    <tableColumn id="3" xr3:uid="{31165455-2AA3-4532-A0A0-C942837C0F79}" name="CA type" dataDxfId="120"/>
-    <tableColumn id="33" xr3:uid="{B83E0E3E-2B28-42F1-BC64-5D7177EC4229}" name="CA Weight" dataDxfId="119"/>
-    <tableColumn id="34" xr3:uid="{AEA2048C-138D-450A-BE52-3FCBDE03C67D}" name="Credits" dataDxfId="118"/>
-    <tableColumn id="30" xr3:uid="{82DD5B5B-C808-4E6E-849C-7A03DC6D0B69}" name="Description" dataDxfId="117"/>
-    <tableColumn id="36" xr3:uid="{A7BF30F6-C808-4B8F-B3FF-9FAF20E2145A}" name="Summative" dataDxfId="116"/>
-    <tableColumn id="37" xr3:uid="{68E504F9-116C-43AB-BCC6-3BB48B0860D2}" name="Day of Week" dataDxfId="115"/>
-    <tableColumn id="16" xr3:uid="{E6637FEB-7F23-45F0-99D2-96D20DD2DAEF}" name="Duration" dataDxfId="114"/>
-    <tableColumn id="31" xr3:uid="{FD1E9614-3960-4F72-BD42-711A4CC7BBA0}" name="Nominal Hours" dataDxfId="113">
+    <tableColumn id="1" xr3:uid="{7078548A-F011-4851-AB36-1F04238FA2FE}" name="Module Code" dataDxfId="89"/>
+    <tableColumn id="2" xr3:uid="{D2290F36-B8B3-427A-AEFE-45FD22901411}" name="Module Title" dataDxfId="88"/>
+    <tableColumn id="3" xr3:uid="{31165455-2AA3-4532-A0A0-C942837C0F79}" name="CA type" dataDxfId="87"/>
+    <tableColumn id="33" xr3:uid="{B83E0E3E-2B28-42F1-BC64-5D7177EC4229}" name="CA Weight" dataDxfId="86"/>
+    <tableColumn id="34" xr3:uid="{AEA2048C-138D-450A-BE52-3FCBDE03C67D}" name="Credits" dataDxfId="85"/>
+    <tableColumn id="30" xr3:uid="{82DD5B5B-C808-4E6E-849C-7A03DC6D0B69}" name="Description" dataDxfId="84"/>
+    <tableColumn id="36" xr3:uid="{A7BF30F6-C808-4B8F-B3FF-9FAF20E2145A}" name="Summative" dataDxfId="83"/>
+    <tableColumn id="37" xr3:uid="{68E504F9-116C-43AB-BCC6-3BB48B0860D2}" name="Day of Week" dataDxfId="82"/>
+    <tableColumn id="16" xr3:uid="{E6637FEB-7F23-45F0-99D2-96D20DD2DAEF}" name="Duration" dataDxfId="81"/>
+    <tableColumn id="31" xr3:uid="{FD1E9614-3960-4F72-BD42-711A4CC7BBA0}" name="Nominal Hours" dataDxfId="80">
       <calculatedColumnFormula>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="32" xr3:uid="{E11C773A-511F-4D25-8636-C56C5B61ED90}" name="Hours" dataDxfId="112"/>
-    <tableColumn id="4" xr3:uid="{04E38F13-8347-412C-866C-6EFE6796253C}" name="Autumn Week 1" dataDxfId="111"/>
-    <tableColumn id="5" xr3:uid="{254D6A24-FC1B-44C7-A3DF-52DA2A250D31}" name="Autumn Week 2" dataDxfId="110"/>
-    <tableColumn id="6" xr3:uid="{9EB326C3-772E-4E56-89FB-BA3A00291293}" name="Autumn Week 3" dataDxfId="109"/>
-    <tableColumn id="7" xr3:uid="{94BC6C78-5A89-4267-B1C1-BFA70E5A9F34}" name="Autumn Week 4" dataDxfId="108"/>
-    <tableColumn id="8" xr3:uid="{CF3B6389-B559-4FE3-8B33-FEDB303382B1}" name="Autumn Week 5" dataDxfId="107"/>
-    <tableColumn id="9" xr3:uid="{8DD80B9C-D1B1-4CDE-A624-4CD3A15113DD}" name="Autumn Week 6" dataDxfId="106"/>
-    <tableColumn id="10" xr3:uid="{8C4EBEE4-01CB-4AD0-B594-F466CC36D370}" name="Autumn Week 7" dataDxfId="105"/>
-    <tableColumn id="11" xr3:uid="{7F8C91DE-BE61-47CF-A916-D06ED7B283E9}" name="Autumn Week 8" dataDxfId="104"/>
-    <tableColumn id="12" xr3:uid="{9D58139A-0F96-4203-8D22-58BC34744B87}" name="Autumn Week 9" dataDxfId="103"/>
-    <tableColumn id="13" xr3:uid="{43C545DF-9B9E-4080-8012-F9EFA0F01283}" name="Autumn Week 10" dataDxfId="102"/>
-    <tableColumn id="14" xr3:uid="{829AB976-2AB2-435C-8F11-DE08DACA4407}" name="Autumn Week 11" dataDxfId="101"/>
-    <tableColumn id="15" xr3:uid="{9126A0EA-FC34-4876-9D56-A0AC39C5526C}" name="Autumn Week 12" dataDxfId="100"/>
-    <tableColumn id="17" xr3:uid="{15B891EE-FCC8-4E53-A90D-3E10FFC1E9FA}" name="Spring Week 1" dataDxfId="99"/>
-    <tableColumn id="18" xr3:uid="{464CA212-3B53-4678-AFE4-8AF8308C1986}" name="Spring Week 2" dataDxfId="98"/>
-    <tableColumn id="19" xr3:uid="{B560E823-CC29-418C-B26C-52D9FFC8C72E}" name="Spring Week 3" dataDxfId="97"/>
-    <tableColumn id="20" xr3:uid="{D95606F3-E0A0-4907-91E0-4AD09D0C65CB}" name="Spring Week 4" dataDxfId="96"/>
-    <tableColumn id="21" xr3:uid="{E71FF892-9A4B-444C-8972-62D92F81B0E7}" name="Spring Week 5" dataDxfId="95"/>
-    <tableColumn id="22" xr3:uid="{C7775BA8-178A-4501-A8DE-2B2CF77A2451}" name="Spring Week 6" dataDxfId="94"/>
-    <tableColumn id="23" xr3:uid="{51A89A97-F839-4F50-88A9-65049D65C9B0}" name="Spring Week 7" dataDxfId="93"/>
-    <tableColumn id="24" xr3:uid="{26EE6D10-4FC4-49AE-8DE6-18AC556C293D}" name="Spring Week 8" dataDxfId="92"/>
-    <tableColumn id="25" xr3:uid="{FCB1B9FB-21DA-415A-86E6-C8E14F864E1B}" name="Spring Week 9" dataDxfId="91"/>
-    <tableColumn id="26" xr3:uid="{54402AE1-DC77-41BA-BCC7-28BCA7186B44}" name="Spring Week 10" dataDxfId="90"/>
-    <tableColumn id="27" xr3:uid="{31C092D1-BD77-4126-8E72-8E74D0D11509}" name="Spring Week 11" dataDxfId="89"/>
-    <tableColumn id="28" xr3:uid="{56D67770-E36A-46FE-97FA-76CD24229C51}" name="Spring Week 12" dataDxfId="88"/>
-    <tableColumn id="38" xr3:uid="{29E08DCE-0D92-40C5-8F33-F1B96FB2F7A4}" name="Spring Exams" dataDxfId="87"/>
-    <tableColumn id="29" xr3:uid="{785AD842-5ED0-4E27-B4B7-26E6FF9AC266}" name="Sub-total" dataDxfId="86">
+    <tableColumn id="32" xr3:uid="{E11C773A-511F-4D25-8636-C56C5B61ED90}" name="Hours" dataDxfId="79"/>
+    <tableColumn id="4" xr3:uid="{04E38F13-8347-412C-866C-6EFE6796253C}" name="Autumn Week 1" dataDxfId="78"/>
+    <tableColumn id="5" xr3:uid="{254D6A24-FC1B-44C7-A3DF-52DA2A250D31}" name="Autumn Week 2" dataDxfId="77"/>
+    <tableColumn id="6" xr3:uid="{9EB326C3-772E-4E56-89FB-BA3A00291293}" name="Autumn Week 3" dataDxfId="76"/>
+    <tableColumn id="7" xr3:uid="{94BC6C78-5A89-4267-B1C1-BFA70E5A9F34}" name="Autumn Week 4" dataDxfId="75"/>
+    <tableColumn id="8" xr3:uid="{CF3B6389-B559-4FE3-8B33-FEDB303382B1}" name="Autumn Week 5" dataDxfId="74"/>
+    <tableColumn id="9" xr3:uid="{8DD80B9C-D1B1-4CDE-A624-4CD3A15113DD}" name="Autumn Week 6" dataDxfId="73"/>
+    <tableColumn id="10" xr3:uid="{8C4EBEE4-01CB-4AD0-B594-F466CC36D370}" name="Autumn Week 7" dataDxfId="72"/>
+    <tableColumn id="11" xr3:uid="{7F8C91DE-BE61-47CF-A916-D06ED7B283E9}" name="Autumn Week 8" dataDxfId="71"/>
+    <tableColumn id="12" xr3:uid="{9D58139A-0F96-4203-8D22-58BC34744B87}" name="Autumn Week 9" dataDxfId="70"/>
+    <tableColumn id="13" xr3:uid="{43C545DF-9B9E-4080-8012-F9EFA0F01283}" name="Autumn Week 10" dataDxfId="69"/>
+    <tableColumn id="14" xr3:uid="{829AB976-2AB2-435C-8F11-DE08DACA4407}" name="Autumn Week 11" dataDxfId="68"/>
+    <tableColumn id="15" xr3:uid="{9126A0EA-FC34-4876-9D56-A0AC39C5526C}" name="Autumn Week 12" dataDxfId="67"/>
+    <tableColumn id="17" xr3:uid="{15B891EE-FCC8-4E53-A90D-3E10FFC1E9FA}" name="Spring Week 1" dataDxfId="66"/>
+    <tableColumn id="18" xr3:uid="{464CA212-3B53-4678-AFE4-8AF8308C1986}" name="Spring Week 2" dataDxfId="65"/>
+    <tableColumn id="19" xr3:uid="{B560E823-CC29-418C-B26C-52D9FFC8C72E}" name="Spring Week 3" dataDxfId="64"/>
+    <tableColumn id="20" xr3:uid="{D95606F3-E0A0-4907-91E0-4AD09D0C65CB}" name="Spring Week 4" dataDxfId="63"/>
+    <tableColumn id="21" xr3:uid="{E71FF892-9A4B-444C-8972-62D92F81B0E7}" name="Spring Week 5" dataDxfId="62"/>
+    <tableColumn id="22" xr3:uid="{C7775BA8-178A-4501-A8DE-2B2CF77A2451}" name="Spring Week 6" dataDxfId="61"/>
+    <tableColumn id="23" xr3:uid="{51A89A97-F839-4F50-88A9-65049D65C9B0}" name="Spring Week 7" dataDxfId="60"/>
+    <tableColumn id="24" xr3:uid="{26EE6D10-4FC4-49AE-8DE6-18AC556C293D}" name="Spring Week 8" dataDxfId="59"/>
+    <tableColumn id="25" xr3:uid="{FCB1B9FB-21DA-415A-86E6-C8E14F864E1B}" name="Spring Week 9" dataDxfId="58"/>
+    <tableColumn id="26" xr3:uid="{54402AE1-DC77-41BA-BCC7-28BCA7186B44}" name="Spring Week 10" dataDxfId="57"/>
+    <tableColumn id="27" xr3:uid="{31C092D1-BD77-4126-8E72-8E74D0D11509}" name="Spring Week 11" dataDxfId="56"/>
+    <tableColumn id="28" xr3:uid="{56D67770-E36A-46FE-97FA-76CD24229C51}" name="Spring Week 12" dataDxfId="55"/>
+    <tableColumn id="38" xr3:uid="{29E08DCE-0D92-40C5-8F33-F1B96FB2F7A4}" name="Spring Exams" dataDxfId="54"/>
+    <tableColumn id="29" xr3:uid="{785AD842-5ED0-4E27-B4B7-26E6FF9AC266}" name="Sub-total" dataDxfId="53">
       <calculatedColumnFormula>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="35" xr3:uid="{EE5D0E71-7823-4EE2-9CC1-32BF500AB742}" name="Total Hours" dataDxfId="85">
+    <tableColumn id="35" xr3:uid="{EE5D0E71-7823-4EE2-9CC1-32BF500AB742}" name="Total Hours" dataDxfId="52">
       <calculatedColumnFormula>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9931,49 +9815,49 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A071F52D-AD51-4120-94C5-67D4117EBD07}" name="Table14" displayName="Table14" ref="A1:AE64" totalsRowShown="0" headerRowDxfId="84" dataDxfId="82" headerRowBorderDxfId="83" tableBorderDxfId="81" totalsRowBorderDxfId="80">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A071F52D-AD51-4120-94C5-67D4117EBD07}" name="Table14" displayName="Table14" ref="A1:AE64" totalsRowShown="0" headerRowDxfId="51" dataDxfId="49" headerRowBorderDxfId="50" tableBorderDxfId="48" totalsRowBorderDxfId="47">
   <autoFilter ref="A1:AE64" xr:uid="{FA69A777-C149-48BD-B248-35F32F0AC920}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AD64">
     <sortCondition ref="A1:A132"/>
   </sortState>
   <tableColumns count="31">
-    <tableColumn id="1" xr3:uid="{D7CE4D57-09F4-4B9D-B464-A087075D1C39}" name="Module Code" dataDxfId="79"/>
-    <tableColumn id="2" xr3:uid="{DE2920B2-70AC-48F3-99E7-07B70BC1E928}" name="Module Title" dataDxfId="78"/>
-    <tableColumn id="3" xr3:uid="{61946E7A-4C82-425B-89A6-3DBD530FCD55}" name="Contact type" dataDxfId="77"/>
-    <tableColumn id="34" xr3:uid="{55A68E2B-9324-4E9E-9629-6611EC7C904E}" name="Credits" dataDxfId="76">
+    <tableColumn id="1" xr3:uid="{D7CE4D57-09F4-4B9D-B464-A087075D1C39}" name="Module Code" dataDxfId="46"/>
+    <tableColumn id="2" xr3:uid="{DE2920B2-70AC-48F3-99E7-07B70BC1E928}" name="Module Title" dataDxfId="45"/>
+    <tableColumn id="3" xr3:uid="{61946E7A-4C82-425B-89A6-3DBD530FCD55}" name="Contact type" dataDxfId="44"/>
+    <tableColumn id="34" xr3:uid="{55A68E2B-9324-4E9E-9629-6611EC7C904E}" name="Credits" dataDxfId="43">
       <calculatedColumnFormula>INDEX(Table2[Credits],MATCH(Table14[[#This Row],[Module Code]],Table2[Module Code],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="30" xr3:uid="{9C4C2C35-CE5A-4469-93FA-21FC6F57EDAD}" name="Semester" dataDxfId="75">
+    <tableColumn id="30" xr3:uid="{9C4C2C35-CE5A-4469-93FA-21FC6F57EDAD}" name="Semester" dataDxfId="42">
       <calculatedColumnFormula>INDEX(Table2[Semester],MATCH(Table14[[#This Row],[Module Code]],Table2[Module Code],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="31" xr3:uid="{A7B09E14-0C35-459D-A9D0-5143D8AFFE4E}" name="Nominal Hours" dataDxfId="74">
+    <tableColumn id="31" xr3:uid="{A7B09E14-0C35-459D-A9D0-5143D8AFFE4E}" name="Nominal Hours" dataDxfId="41">
       <calculatedColumnFormula>INDEX(Table2[Contact Time],MATCH(Table14[[#This Row],[Module Code]],Table2[Module Code],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{503822B3-8862-4FCD-9DD3-3B52F57A97BE}" name="Autumn Week 1" dataDxfId="73"/>
-    <tableColumn id="5" xr3:uid="{760391D0-3219-4B11-8E3D-3E00EEDFA9DD}" name="Autumn Week 2" dataDxfId="72"/>
-    <tableColumn id="6" xr3:uid="{6EE5E3E9-C4FB-49BE-932C-B84EA0A7970D}" name="Autumn Week 3" dataDxfId="71"/>
-    <tableColumn id="7" xr3:uid="{2C7AD515-480E-49A6-8076-95205ACF95EC}" name="Autumn Week 4" dataDxfId="70"/>
-    <tableColumn id="8" xr3:uid="{6FD8C5C6-433E-493B-BB28-5ADD15CFC7FB}" name="Autumn Week 5" dataDxfId="69"/>
-    <tableColumn id="9" xr3:uid="{801E6BE2-75F8-40A5-A263-0AAEFDAA63E7}" name="Autumn Week 6" dataDxfId="68"/>
-    <tableColumn id="10" xr3:uid="{976D463A-C6BC-4636-B732-53E6CDF3F6C7}" name="Autumn Week 7" dataDxfId="67"/>
-    <tableColumn id="11" xr3:uid="{D025F987-6302-4D7B-9A9A-636F867D1872}" name="Autumn Week 8" dataDxfId="66"/>
-    <tableColumn id="12" xr3:uid="{D30D10EE-2DE5-4659-AA67-2134D11D6119}" name="Autumn Week 9" dataDxfId="65"/>
-    <tableColumn id="13" xr3:uid="{35E8F713-2D13-47B7-9811-293DA89F0D62}" name="Autumn Week 10" dataDxfId="64"/>
-    <tableColumn id="14" xr3:uid="{5DD48606-F817-4B30-8BA1-A96457CBB489}" name="Autumn Week 11" dataDxfId="63"/>
-    <tableColumn id="15" xr3:uid="{9B982ED1-A4C5-4E87-99AB-70713F2B634E}" name="Autumn Week 12" dataDxfId="62"/>
-    <tableColumn id="17" xr3:uid="{3AFDFF11-D351-428A-AC16-E674EB9DD7CC}" name="Spring Week 1" dataDxfId="61"/>
-    <tableColumn id="18" xr3:uid="{1431E9F9-328E-4229-9377-39D94C660D67}" name="Spring Week 2" dataDxfId="60"/>
-    <tableColumn id="19" xr3:uid="{8E1051DB-2A93-4ABA-8317-8F9921CF483D}" name="Spring Week 3" dataDxfId="59"/>
-    <tableColumn id="20" xr3:uid="{98B745E4-C481-42FF-9D3B-0D0899BD3DB6}" name="Spring Week 4" dataDxfId="58"/>
-    <tableColumn id="21" xr3:uid="{2FC9B562-4622-444D-9372-5637BFE48E0A}" name="Spring Week 5" dataDxfId="57"/>
-    <tableColumn id="22" xr3:uid="{95778D77-82F1-4B00-8FED-6FEB2BF83C3D}" name="Spring Week 6" dataDxfId="56"/>
-    <tableColumn id="23" xr3:uid="{9A49A64C-9A09-47A0-BC65-A8C1C98DACA3}" name="Spring Week 7" dataDxfId="55"/>
-    <tableColumn id="24" xr3:uid="{191AACBA-3CF0-48E5-B522-FCD2CCE9AC99}" name="Spring Week 8" dataDxfId="54"/>
-    <tableColumn id="25" xr3:uid="{DC35B6C1-904B-4E6A-A04F-ADF850A50D85}" name="Spring Week 9" dataDxfId="53"/>
-    <tableColumn id="26" xr3:uid="{BEB9E86A-57BF-4A1E-A499-BADB9EAD1DE9}" name="Spring Week 10" dataDxfId="52"/>
-    <tableColumn id="27" xr3:uid="{D640FB81-F093-4E3F-B7A1-6995DDDD6305}" name="Spring Week 11" dataDxfId="51"/>
-    <tableColumn id="28" xr3:uid="{496FDC17-F0F2-4381-96DA-177DC578A786}" name="Spring Week 12" dataDxfId="50"/>
-    <tableColumn id="32" xr3:uid="{65BCC67A-5DC9-4957-BB42-BCF5FCA71B17}" name="Total" dataDxfId="49">
+    <tableColumn id="4" xr3:uid="{503822B3-8862-4FCD-9DD3-3B52F57A97BE}" name="Autumn Week 1" dataDxfId="40"/>
+    <tableColumn id="5" xr3:uid="{760391D0-3219-4B11-8E3D-3E00EEDFA9DD}" name="Autumn Week 2" dataDxfId="39"/>
+    <tableColumn id="6" xr3:uid="{6EE5E3E9-C4FB-49BE-932C-B84EA0A7970D}" name="Autumn Week 3" dataDxfId="38"/>
+    <tableColumn id="7" xr3:uid="{2C7AD515-480E-49A6-8076-95205ACF95EC}" name="Autumn Week 4" dataDxfId="37"/>
+    <tableColumn id="8" xr3:uid="{6FD8C5C6-433E-493B-BB28-5ADD15CFC7FB}" name="Autumn Week 5" dataDxfId="36"/>
+    <tableColumn id="9" xr3:uid="{801E6BE2-75F8-40A5-A263-0AAEFDAA63E7}" name="Autumn Week 6" dataDxfId="35"/>
+    <tableColumn id="10" xr3:uid="{976D463A-C6BC-4636-B732-53E6CDF3F6C7}" name="Autumn Week 7" dataDxfId="34"/>
+    <tableColumn id="11" xr3:uid="{D025F987-6302-4D7B-9A9A-636F867D1872}" name="Autumn Week 8" dataDxfId="33"/>
+    <tableColumn id="12" xr3:uid="{D30D10EE-2DE5-4659-AA67-2134D11D6119}" name="Autumn Week 9" dataDxfId="32"/>
+    <tableColumn id="13" xr3:uid="{35E8F713-2D13-47B7-9811-293DA89F0D62}" name="Autumn Week 10" dataDxfId="31"/>
+    <tableColumn id="14" xr3:uid="{5DD48606-F817-4B30-8BA1-A96457CBB489}" name="Autumn Week 11" dataDxfId="30"/>
+    <tableColumn id="15" xr3:uid="{9B982ED1-A4C5-4E87-99AB-70713F2B634E}" name="Autumn Week 12" dataDxfId="29"/>
+    <tableColumn id="17" xr3:uid="{3AFDFF11-D351-428A-AC16-E674EB9DD7CC}" name="Spring Week 1" dataDxfId="28"/>
+    <tableColumn id="18" xr3:uid="{1431E9F9-328E-4229-9377-39D94C660D67}" name="Spring Week 2" dataDxfId="27"/>
+    <tableColumn id="19" xr3:uid="{8E1051DB-2A93-4ABA-8317-8F9921CF483D}" name="Spring Week 3" dataDxfId="26"/>
+    <tableColumn id="20" xr3:uid="{98B745E4-C481-42FF-9D3B-0D0899BD3DB6}" name="Spring Week 4" dataDxfId="25"/>
+    <tableColumn id="21" xr3:uid="{2FC9B562-4622-444D-9372-5637BFE48E0A}" name="Spring Week 5" dataDxfId="24"/>
+    <tableColumn id="22" xr3:uid="{95778D77-82F1-4B00-8FED-6FEB2BF83C3D}" name="Spring Week 6" dataDxfId="23"/>
+    <tableColumn id="23" xr3:uid="{9A49A64C-9A09-47A0-BC65-A8C1C98DACA3}" name="Spring Week 7" dataDxfId="22"/>
+    <tableColumn id="24" xr3:uid="{191AACBA-3CF0-48E5-B522-FCD2CCE9AC99}" name="Spring Week 8" dataDxfId="21"/>
+    <tableColumn id="25" xr3:uid="{DC35B6C1-904B-4E6A-A04F-ADF850A50D85}" name="Spring Week 9" dataDxfId="20"/>
+    <tableColumn id="26" xr3:uid="{BEB9E86A-57BF-4A1E-A499-BADB9EAD1DE9}" name="Spring Week 10" dataDxfId="19"/>
+    <tableColumn id="27" xr3:uid="{D640FB81-F093-4E3F-B7A1-6995DDDD6305}" name="Spring Week 11" dataDxfId="18"/>
+    <tableColumn id="28" xr3:uid="{496FDC17-F0F2-4381-96DA-177DC578A786}" name="Spring Week 12" dataDxfId="17"/>
+    <tableColumn id="32" xr3:uid="{65BCC67A-5DC9-4957-BB42-BCF5FCA71B17}" name="Total" dataDxfId="16">
       <calculatedColumnFormula>SUM(Table14[[#This Row],[Autumn Week 1]:[Spring Week 12]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9982,38 +9866,38 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4070B5A2-579F-42D6-AF31-642FC3F016DD}" name="Table2" displayName="Table2" ref="A1:X109" totalsRowShown="0" headerRowDxfId="48" dataDxfId="46" headerRowBorderDxfId="47">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4070B5A2-579F-42D6-AF31-642FC3F016DD}" name="Table2" displayName="Table2" ref="A1:X109" totalsRowShown="0" headerRowDxfId="116" dataDxfId="114" headerRowBorderDxfId="115">
   <autoFilter ref="A1:X109" xr:uid="{4070B5A2-579F-42D6-AF31-642FC3F016DD}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B64">
     <sortCondition ref="A1:A64"/>
   </sortState>
   <tableColumns count="24">
-    <tableColumn id="1" xr3:uid="{A36A2B86-0F30-4188-9ECD-AE5BC71A59F4}" name="Module Code" dataDxfId="45"/>
-    <tableColumn id="2" xr3:uid="{D3F20037-EF35-4207-A530-484E1EB45719}" name="Module Title" dataDxfId="44"/>
-    <tableColumn id="9" xr3:uid="{40C22022-10B9-411F-9B76-B89140ABFFB2}" name="Alternative Module Code" dataDxfId="43"/>
-    <tableColumn id="13" xr3:uid="{CB12E405-1802-457C-AF17-F1B9CB3BBF13}" name="Source" dataDxfId="42"/>
-    <tableColumn id="8" xr3:uid="{EA737976-1AA7-49B6-8752-A388621554F4}" name="Semester" dataDxfId="41"/>
-    <tableColumn id="6" xr3:uid="{16DFC84F-5858-467D-B447-49992D721E4B}" name="Level" dataDxfId="40"/>
-    <tableColumn id="5" xr3:uid="{A17BC4BA-A3CB-442D-9BDC-D3B41B98B389}" name="Credits" dataDxfId="39"/>
-    <tableColumn id="24" xr3:uid="{BB8B1D0C-7F1D-4DB4-BBCE-55FD0E53BFE2}" name="Parent" dataDxfId="28"/>
-    <tableColumn id="19" xr3:uid="{98846C13-E462-4CFF-858E-AF75931B6712}" name="AllUG" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{7E25B4F4-1A7D-48D9-AAA2-AF5C97240797}" name="Physics" dataDxfId="38"/>
+    <tableColumn id="1" xr3:uid="{A36A2B86-0F30-4188-9ECD-AE5BC71A59F4}" name="Module Code" dataDxfId="113"/>
+    <tableColumn id="2" xr3:uid="{D3F20037-EF35-4207-A530-484E1EB45719}" name="Module Title" dataDxfId="112"/>
+    <tableColumn id="9" xr3:uid="{40C22022-10B9-411F-9B76-B89140ABFFB2}" name="Alternative Module Code" dataDxfId="111"/>
+    <tableColumn id="13" xr3:uid="{CB12E405-1802-457C-AF17-F1B9CB3BBF13}" name="Source" dataDxfId="110"/>
+    <tableColumn id="8" xr3:uid="{EA737976-1AA7-49B6-8752-A388621554F4}" name="Semester" dataDxfId="109"/>
+    <tableColumn id="6" xr3:uid="{16DFC84F-5858-467D-B447-49992D721E4B}" name="Level" dataDxfId="108"/>
+    <tableColumn id="5" xr3:uid="{A17BC4BA-A3CB-442D-9BDC-D3B41B98B389}" name="Credits" dataDxfId="107"/>
+    <tableColumn id="24" xr3:uid="{BB8B1D0C-7F1D-4DB4-BBCE-55FD0E53BFE2}" name="Parent" dataDxfId="106"/>
+    <tableColumn id="19" xr3:uid="{98846C13-E462-4CFF-858E-AF75931B6712}" name="AllUG" dataDxfId="105"/>
+    <tableColumn id="3" xr3:uid="{7E25B4F4-1A7D-48D9-AAA2-AF5C97240797}" name="Physics" dataDxfId="104"/>
     <tableColumn id="17" xr3:uid="{AA3AE96F-2651-49D7-89AD-BA94806438AE}" name="PhysAstro"/>
-    <tableColumn id="4" xr3:uid="{9C7DD469-E550-411F-8467-246A1543FB38}" name="Astro" dataDxfId="37"/>
-    <tableColumn id="7" xr3:uid="{3C5D3AEB-487E-4678-A42F-BE4BA4D0E9AA}" name="MedPhys" dataDxfId="36"/>
+    <tableColumn id="4" xr3:uid="{9C7DD469-E550-411F-8467-246A1543FB38}" name="Astro" dataDxfId="103"/>
+    <tableColumn id="7" xr3:uid="{3C5D3AEB-487E-4678-A42F-BE4BA4D0E9AA}" name="MedPhys" dataDxfId="102"/>
     <tableColumn id="20" xr3:uid="{C3673B06-C0A2-44F6-8978-F392282CECF8}" name="AllPG"/>
-    <tableColumn id="14" xr3:uid="{AE552873-9B31-41A6-B73C-D052477CA74C}" name="MScPhysics" dataDxfId="35"/>
-    <tableColumn id="15" xr3:uid="{8F51CE76-3A29-487A-A13C-FB63C79CF3E6}" name="MScAstro" dataDxfId="34"/>
-    <tableColumn id="21" xr3:uid="{FC74E264-78AB-4682-A1B8-D8964ED1C3F3}" name="MScDataPhys" dataDxfId="33"/>
-    <tableColumn id="22" xr3:uid="{2D5776F7-D7F7-4D20-A7CB-DB57997AD074}" name="MScDataAstro" dataDxfId="32"/>
+    <tableColumn id="14" xr3:uid="{AE552873-9B31-41A6-B73C-D052477CA74C}" name="MScPhysics" dataDxfId="101"/>
+    <tableColumn id="15" xr3:uid="{8F51CE76-3A29-487A-A13C-FB63C79CF3E6}" name="MScAstro" dataDxfId="100"/>
+    <tableColumn id="21" xr3:uid="{FC74E264-78AB-4682-A1B8-D8964ED1C3F3}" name="MScDataPhys" dataDxfId="99"/>
+    <tableColumn id="22" xr3:uid="{2D5776F7-D7F7-4D20-A7CB-DB57997AD074}" name="MScDataAstro" dataDxfId="98"/>
     <tableColumn id="18" xr3:uid="{10668F71-1EDF-482E-86A5-46E1F3C15120}" name="MScCSPhysics"/>
     <tableColumn id="23" xr3:uid="{E837FCBC-49C7-45CE-AFAA-4F01143EF2A8}" name="CDTCSPhysics"/>
     <tableColumn id="16" xr3:uid="{DB790F5F-BEF0-41CE-A68A-1AA9DF83D66B}" name="Contact Time"/>
-    <tableColumn id="10" xr3:uid="{60774AFA-B365-4EB5-AAFF-6235868F8C97}" name="Exam Weight (%)" dataDxfId="31"/>
-    <tableColumn id="12" xr3:uid="{537B7C75-E9C0-42F2-9F3C-6E960AB2D257}" name="CA weight" dataDxfId="30">
+    <tableColumn id="10" xr3:uid="{60774AFA-B365-4EB5-AAFF-6235868F8C97}" name="Exam Weight (%)" dataDxfId="97"/>
+    <tableColumn id="12" xr3:uid="{537B7C75-E9C0-42F2-9F3C-6E960AB2D257}" name="CA weight" dataDxfId="96">
       <calculatedColumnFormula>100-Table2[[#This Row],[Exam Weight (%)]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{75DA2527-5A08-4ECE-B4E4-752A8F8BF059}" name="CA Check" dataDxfId="29">
+    <tableColumn id="11" xr3:uid="{75DA2527-5A08-4ECE-B4E4-752A8F8BF059}" name="CA Check" dataDxfId="95">
       <calculatedColumnFormula>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -32592,7 +32476,7 @@
       </c>
       <c r="L32" s="6"/>
       <c r="M32" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N32" s="6"/>
       <c r="O32" s="6"/>
@@ -33321,13 +33205,13 @@
       </c>
     </row>
     <row r="46" spans="1:24">
-      <c r="A46" s="54" t="s">
+      <c r="A46" s="3" t="s">
         <v>395</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="C46" s="54"/>
+      <c r="C46" s="3"/>
       <c r="D46" s="2" t="s">
         <v>180</v>
       </c>
@@ -33340,35 +33224,30 @@
       <c r="G46" s="2">
         <v>30</v>
       </c>
-      <c r="H46" s="56" t="s">
+      <c r="H46" s="28" t="s">
         <v>395</v>
       </c>
       <c r="I46" s="28"/>
       <c r="L46" t="s">
         <v>143</v>
       </c>
-      <c r="O46" s="57"/>
-      <c r="P46" s="57"/>
-      <c r="Q46" s="57"/>
-      <c r="R46" s="57"/>
-      <c r="V46" s="57"/>
-      <c r="W46" s="58">
+      <c r="W46">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="X46" s="58">
+      <c r="X46">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:24">
-      <c r="A47" s="54" t="s">
+      <c r="A47" s="3" t="s">
         <v>396</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="C47" s="54"/>
+      <c r="C47" s="3"/>
       <c r="D47" s="2" t="s">
         <v>180</v>
       </c>
@@ -33381,23 +33260,18 @@
       <c r="G47" s="2">
         <v>30</v>
       </c>
-      <c r="H47" s="56" t="s">
+      <c r="H47" s="28" t="s">
         <v>47</v>
       </c>
       <c r="I47" s="28"/>
       <c r="M47" t="s">
         <v>143</v>
       </c>
-      <c r="O47" s="57"/>
-      <c r="P47" s="57"/>
-      <c r="Q47" s="57"/>
-      <c r="R47" s="57"/>
-      <c r="V47" s="57"/>
-      <c r="W47" s="58">
+      <c r="W47">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="X47" s="58">
+      <c r="X47">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>0</v>
       </c>
@@ -34370,13 +34244,13 @@
       </c>
     </row>
     <row r="65" spans="1:24">
-      <c r="A65" s="54" t="s">
+      <c r="A65" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="B65" s="54" t="s">
+      <c r="B65" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="C65" s="54"/>
+      <c r="C65" s="3"/>
       <c r="D65" s="2" t="s">
         <v>180</v>
       </c>
@@ -34398,19 +34272,18 @@
       </c>
       <c r="M65" s="6"/>
       <c r="N65" s="6"/>
-      <c r="O65" s="59"/>
-      <c r="P65" s="59"/>
-      <c r="Q65" s="59"/>
-      <c r="R65" s="59"/>
+      <c r="O65" s="6"/>
+      <c r="P65" s="6"/>
+      <c r="Q65" s="6"/>
+      <c r="R65" s="6"/>
       <c r="S65" s="6"/>
       <c r="T65" s="6"/>
       <c r="U65" s="6"/>
-      <c r="V65" s="57"/>
-      <c r="W65" s="58">
+      <c r="W65">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="X65" s="58">
+      <c r="X65">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>0</v>
       </c>
@@ -36367,187 +36240,139 @@
       </c>
     </row>
     <row r="104" spans="1:24">
-      <c r="A104" s="54" t="s">
+      <c r="A104" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="B104" s="54" t="s">
+      <c r="B104" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="C104" s="54"/>
+      <c r="C104" s="3"/>
       <c r="D104" s="28"/>
-      <c r="E104" s="54"/>
-      <c r="F104" s="55"/>
-      <c r="G104" s="56"/>
+      <c r="E104" s="3"/>
+      <c r="F104" s="4"/>
+      <c r="G104" s="28"/>
       <c r="H104" s="28"/>
       <c r="I104" s="28"/>
-      <c r="J104" s="57"/>
-      <c r="L104" s="57"/>
-      <c r="M104" s="57"/>
-      <c r="O104" s="57"/>
-      <c r="P104" s="57"/>
-      <c r="Q104" s="57"/>
-      <c r="R104" s="57"/>
-      <c r="V104" s="57"/>
-      <c r="W104" s="58">
+      <c r="W104">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="X104" s="58">
+      <c r="X104">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:24">
-      <c r="A105" s="54" t="s">
+      <c r="A105" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="B105" s="54" t="s">
+      <c r="B105" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="C105" s="54"/>
+      <c r="C105" s="3"/>
       <c r="D105" s="28"/>
-      <c r="E105" s="54"/>
-      <c r="F105" s="55"/>
-      <c r="G105" s="56"/>
+      <c r="E105" s="3"/>
+      <c r="F105" s="4"/>
+      <c r="G105" s="28"/>
       <c r="H105" s="28"/>
       <c r="I105" s="28"/>
-      <c r="J105" s="57"/>
-      <c r="L105" s="57"/>
-      <c r="M105" s="57"/>
-      <c r="O105" s="57"/>
-      <c r="P105" s="57"/>
-      <c r="Q105" s="57"/>
-      <c r="R105" s="57"/>
-      <c r="V105" s="57"/>
-      <c r="W105" s="58">
+      <c r="W105">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="X105" s="58">
+      <c r="X105">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:24">
-      <c r="A106" s="54" t="s">
+      <c r="A106" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="B106" s="54" t="s">
+      <c r="B106" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="C106" s="54"/>
+      <c r="C106" s="3"/>
       <c r="D106" s="28"/>
-      <c r="E106" s="54"/>
-      <c r="F106" s="55"/>
-      <c r="G106" s="56"/>
+      <c r="E106" s="3"/>
+      <c r="F106" s="4"/>
+      <c r="G106" s="28"/>
       <c r="H106" s="28"/>
       <c r="I106" s="28"/>
-      <c r="J106" s="57"/>
-      <c r="L106" s="57"/>
-      <c r="M106" s="57"/>
-      <c r="O106" s="57"/>
-      <c r="P106" s="57"/>
-      <c r="Q106" s="57"/>
-      <c r="R106" s="57"/>
-      <c r="V106" s="57"/>
-      <c r="W106" s="58">
+      <c r="W106">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="X106" s="58">
+      <c r="X106">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:24">
-      <c r="A107" s="54" t="s">
+      <c r="A107" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="B107" s="54" t="s">
+      <c r="B107" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="C107" s="54"/>
+      <c r="C107" s="3"/>
       <c r="D107" s="28"/>
-      <c r="E107" s="54"/>
-      <c r="F107" s="55"/>
-      <c r="G107" s="56"/>
+      <c r="E107" s="3"/>
+      <c r="F107" s="4"/>
+      <c r="G107" s="28"/>
       <c r="H107" s="28"/>
       <c r="I107" s="28"/>
-      <c r="J107" s="57"/>
-      <c r="L107" s="57"/>
-      <c r="M107" s="57"/>
-      <c r="O107" s="57"/>
-      <c r="P107" s="57"/>
-      <c r="Q107" s="57"/>
-      <c r="R107" s="57"/>
-      <c r="V107" s="57"/>
-      <c r="W107" s="58">
+      <c r="W107">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="X107" s="58">
+      <c r="X107">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:24">
-      <c r="A108" s="54" t="s">
+      <c r="A108" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="B108" s="54" t="s">
+      <c r="B108" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="C108" s="54"/>
+      <c r="C108" s="3"/>
       <c r="D108" s="28"/>
-      <c r="E108" s="54"/>
-      <c r="F108" s="55"/>
-      <c r="G108" s="56"/>
+      <c r="E108" s="3"/>
+      <c r="F108" s="4"/>
+      <c r="G108" s="28"/>
       <c r="H108" s="28"/>
       <c r="I108" s="28"/>
-      <c r="J108" s="57"/>
-      <c r="L108" s="57"/>
-      <c r="M108" s="57"/>
-      <c r="O108" s="57"/>
-      <c r="P108" s="57"/>
-      <c r="Q108" s="57"/>
-      <c r="R108" s="57"/>
-      <c r="V108" s="57"/>
-      <c r="W108" s="58">
+      <c r="W108">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="X108" s="58">
+      <c r="X108">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:24">
-      <c r="A109" s="54" t="s">
+      <c r="A109" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="B109" s="54" t="s">
+      <c r="B109" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="C109" s="54"/>
+      <c r="C109" s="3"/>
       <c r="D109" s="28"/>
-      <c r="E109" s="54"/>
-      <c r="F109" s="55"/>
-      <c r="G109" s="56"/>
+      <c r="E109" s="3"/>
+      <c r="F109" s="4"/>
+      <c r="G109" s="28"/>
       <c r="H109" s="28"/>
       <c r="I109" s="28"/>
-      <c r="J109" s="57"/>
-      <c r="L109" s="57"/>
-      <c r="M109" s="57"/>
-      <c r="O109" s="57"/>
-      <c r="P109" s="57"/>
-      <c r="Q109" s="57"/>
-      <c r="R109" s="57"/>
-      <c r="V109" s="57"/>
-      <c r="W109" s="58">
+      <c r="W109">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
       </c>
-      <c r="X109" s="58">
+      <c r="X109">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
         <v>0</v>
       </c>
@@ -36648,24 +36473,24 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E2:E109">
-    <cfRule type="containsText" dxfId="27" priority="19" operator="containsText" text="SEMD">
+    <cfRule type="containsText" dxfId="15" priority="19" operator="containsText" text="SEMD">
       <formula>NOT(ISERROR(SEARCH("SEMD",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="26" priority="20" operator="containsText" text="SEM2">
+    <cfRule type="containsText" dxfId="14" priority="20" operator="containsText" text="SEM2">
       <formula>NOT(ISERROR(SEARCH("SEM2",E2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="25" priority="21" operator="containsText" text="SEM1">
+    <cfRule type="containsText" dxfId="13" priority="21" operator="containsText" text="SEM1">
       <formula>NOT(ISERROR(SEARCH("SEM1",E2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E99:E103">
-    <cfRule type="containsText" dxfId="24" priority="11" operator="containsText" text="SEMD">
+    <cfRule type="containsText" dxfId="12" priority="11" operator="containsText" text="SEMD">
       <formula>NOT(ISERROR(SEARCH("SEMD",E99)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="23" priority="12" operator="containsText" text="SEM2">
+    <cfRule type="containsText" dxfId="11" priority="12" operator="containsText" text="SEM2">
       <formula>NOT(ISERROR(SEARCH("SEM2",E99)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="22" priority="13" operator="containsText" text="SEM1">
+    <cfRule type="containsText" dxfId="10" priority="13" operator="containsText" text="SEM1">
       <formula>NOT(ISERROR(SEARCH("SEM1",E99)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -36713,33 +36538,33 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N99:T103 N2:U98">
-    <cfRule type="containsText" dxfId="21" priority="23" operator="containsText" text="O">
+  <conditionalFormatting sqref="I2:M109">
+    <cfRule type="containsText" dxfId="9" priority="2" operator="containsText" text="O">
+      <formula>NOT(ISERROR(SEARCH("O",I2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="8" priority="3" operator="containsText" text="C">
+      <formula>NOT(ISERROR(SEARCH("C",I2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N2:U98 N99:T103">
+    <cfRule type="containsText" dxfId="5" priority="23" operator="containsText" text="O">
       <formula>NOT(ISERROR(SEARCH("O",N2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="20" priority="24" operator="containsText" text="C">
+    <cfRule type="containsText" dxfId="4" priority="24" operator="containsText" text="C">
       <formula>NOT(ISERROR(SEARCH("C",N2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U99:U103">
-    <cfRule type="containsText" dxfId="17" priority="9" operator="containsText" text="O">
+    <cfRule type="containsText" dxfId="2" priority="9" operator="containsText" text="O">
       <formula>NOT(ISERROR(SEARCH("O",U99)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="16" priority="10" operator="containsText" text="C">
+    <cfRule type="containsText" dxfId="1" priority="10" operator="containsText" text="C">
       <formula>NOT(ISERROR(SEARCH("C",U99)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:X109">
-    <cfRule type="expression" dxfId="15" priority="16">
+    <cfRule type="expression" dxfId="0" priority="16">
       <formula>X2&lt;&gt;W2</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I2:M109">
-    <cfRule type="containsText" dxfId="10" priority="2" operator="containsText" text="O">
-      <formula>NOT(ISERROR(SEARCH("O",I2)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="C">
-      <formula>NOT(ISERROR(SEARCH("C",I2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -36750,6 +36575,20 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{611DB1DB-AE5D-4557-A9D5-505B18ADA866}">
+            <xm:f>NOT(ISERROR(SEARCH("-",J2)))</xm:f>
+            <xm:f>"-"</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor theme="0" tint="-0.24994659260841701"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>J2:M109</xm:sqref>
+        </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="containsText" priority="17" operator="containsText" id="{AB48118A-1CFE-488B-B12E-453EA0CADD16}">
             <xm:f>NOT(ISERROR(SEARCH("-",N2)))</xm:f>
@@ -36778,20 +36617,6 @@
           </x14:cfRule>
           <xm:sqref>U99:U103</xm:sqref>
         </x14:conditionalFormatting>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{611DB1DB-AE5D-4557-A9D5-505B18ADA866}">
-            <xm:f>NOT(ISERROR(SEARCH("-",J2)))</xm:f>
-            <xm:f>"-"</xm:f>
-            <x14:dxf>
-              <fill>
-                <patternFill>
-                  <bgColor theme="0" tint="-0.24994659260841701"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <xm:sqref>J2:M109</xm:sqref>
-        </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
   </extLst>

--- a/AssessmentSchedule_2627_v2.xlsx
+++ b/AssessmentSchedule_2627_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cf-my.sharepoint.com/personal/northce_cardiff_ac_uk/Documents/Documents/Cardiff/DUGS/Assessments/Schedule Modelling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="231" documentId="8_{0C641013-E594-4AA6-B777-C2C249EA34A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E1A89C6-7BA3-4DA9-9090-5E52E58D2FD5}"/>
+  <xr:revisionPtr revIDLastSave="235" documentId="8_{0C641013-E594-4AA6-B777-C2C249EA34A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{357115BB-E968-45F9-A82B-E04E8F53CDFD}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A20BCC1C-F123-4C76-9181-B345A7D760BE}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{A20BCC1C-F123-4C76-9181-B345A7D760BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Assessments" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId5"/>
+    <pivotCache cacheId="5" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2953" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2953" uniqueCount="416">
   <si>
     <t>Module Code</t>
   </si>
@@ -1301,6 +1301,12 @@
   </si>
   <si>
     <t>Quiz (old)</t>
+  </si>
+  <si>
+    <t>Fr (*)</t>
+  </si>
+  <si>
+    <t>Problem Sheets</t>
   </si>
 </sst>
 </file>
@@ -9299,7 +9305,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3F344565-A902-475D-ACD8-7DA2FB255CBD}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3F344565-A902-475D-ACD8-7DA2FB255CBD}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:B70" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
   <pivotFields count="34">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -10212,21 +10218,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66039B40-29AD-4D93-B125-EAF72A7B3996}">
   <dimension ref="A1:AL185"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14.81640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="50.81640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.796875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.796875" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="10" style="10" customWidth="1"/>
-    <col min="6" max="6" width="21.7265625" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="21.7265625" style="10" customWidth="1"/>
-    <col min="9" max="9" width="10.7265625" style="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="10.7265625" style="10" customWidth="1"/>
-    <col min="12" max="23" width="9.1796875" style="14" customWidth="1"/>
-    <col min="24" max="36" width="9.1796875" style="16" customWidth="1"/>
+    <col min="6" max="6" width="21.73046875" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="21.73046875" style="10" customWidth="1"/>
+    <col min="9" max="9" width="10.73046875" style="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="10.73046875" style="10" customWidth="1"/>
+    <col min="12" max="23" width="9.19921875" style="14" customWidth="1"/>
+    <col min="24" max="36" width="9.19921875" style="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" s="44" customFormat="1" ht="29">
+    <row r="1" spans="1:38" s="44" customFormat="1" ht="28.5">
       <c r="A1" s="39" t="s">
         <v>0</v>
       </c>
@@ -10640,7 +10646,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:38" ht="28">
+    <row r="6" spans="1:38" ht="27">
       <c r="A6" s="4" t="s">
         <v>252</v>
       </c>
@@ -11221,7 +11227,7 @@
         <v>29.6</v>
       </c>
     </row>
-    <row r="13" spans="1:38" ht="28">
+    <row r="13" spans="1:38" ht="27">
       <c r="A13" s="3" t="s">
         <v>81</v>
       </c>
@@ -11997,7 +12003,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:38" ht="28">
+    <row r="23" spans="1:38" ht="27">
       <c r="A23" s="4" t="s">
         <v>37</v>
       </c>
@@ -12246,72 +12252,66 @@
     </row>
     <row r="26" spans="1:38">
       <c r="A26" s="4" t="s">
-        <v>234</v>
+        <v>258</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="C26" s="11" t="s">
         <v>5</v>
       </c>
       <c r="D26" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="E26" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
       <c r="F26" s="11" t="s">
-        <v>351</v>
+        <v>415</v>
       </c>
       <c r="G26" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="I26" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J26" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>0.39999999999999991</v>
-      </c>
-      <c r="K26" s="11">
-        <v>1</v>
-      </c>
-      <c r="L26" s="18">
-        <v>0.01</v>
-      </c>
-      <c r="M26" s="18">
-        <v>0.01</v>
-      </c>
+        <v>2.6666666666666665</v>
+      </c>
+      <c r="K26" s="11"/>
+      <c r="L26" s="18"/>
+      <c r="M26" s="18"/>
       <c r="N26" s="18">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="O26" s="18">
-        <v>0.01</v>
+        <v>-3.5000000000000003E-2</v>
       </c>
       <c r="P26" s="18">
-        <v>0.01</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="Q26" s="18">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="R26" s="18">
-        <v>0.01</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="S26" s="18">
-        <v>0.01</v>
-      </c>
-      <c r="T26" s="18">
-        <v>0.01</v>
-      </c>
+        <v>-0.03</v>
+      </c>
+      <c r="T26" s="18"/>
       <c r="U26" s="18">
-        <v>0.01</v>
-      </c>
-      <c r="V26" s="18"/>
+        <v>-2.5000000000000001E-2</v>
+      </c>
+      <c r="V26" s="18">
+        <v>-2.5000000000000001E-2</v>
+      </c>
       <c r="W26" s="19"/>
       <c r="X26" s="20"/>
       <c r="Y26" s="20"/>
@@ -12328,39 +12328,39 @@
       <c r="AJ26" s="20"/>
       <c r="AK26" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>9.9999999999999992E-2</v>
+        <v>0.2</v>
       </c>
       <c r="AL26" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:38">
       <c r="A27" s="4" t="s">
-        <v>234</v>
+        <v>258</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>235</v>
+        <v>257</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>5</v>
+        <v>121</v>
       </c>
       <c r="D27" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="E27" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>343</v>
+        <v>263</v>
       </c>
       <c r="G27" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>298</v>
+        <v>414</v>
       </c>
       <c r="I27" s="11">
         <v>3</v>
@@ -12370,7 +12370,7 @@
         <v>8</v>
       </c>
       <c r="K27" s="11">
-        <v>15</v>
+        <v>0.5</v>
       </c>
       <c r="L27" s="18"/>
       <c r="M27" s="18"/>
@@ -12378,15 +12378,13 @@
       <c r="O27" s="19"/>
       <c r="P27" s="18"/>
       <c r="Q27" s="18"/>
-      <c r="R27" s="18">
+      <c r="R27" s="18"/>
+      <c r="S27" s="19"/>
+      <c r="T27" s="18">
         <v>0.2</v>
       </c>
-      <c r="S27" s="19"/>
-      <c r="T27" s="18"/>
       <c r="U27" s="18"/>
-      <c r="V27" s="18">
-        <v>0.2</v>
-      </c>
+      <c r="V27" s="18"/>
       <c r="W27" s="19"/>
       <c r="X27" s="20"/>
       <c r="Y27" s="20"/>
@@ -12403,11 +12401,11 @@
       <c r="AJ27" s="20"/>
       <c r="AK27" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="AL27" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>30</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="28" spans="1:38">
@@ -12418,7 +12416,7 @@
         <v>235</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D28" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
@@ -12429,38 +12427,56 @@
         <v>10</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>267</v>
+        <v>351</v>
       </c>
       <c r="G28" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="I28" s="11">
         <v>1</v>
       </c>
       <c r="J28" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>20</v>
+        <v>0.39999999999999991</v>
       </c>
       <c r="K28" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="L28" s="18"/>
-      <c r="M28" s="18"/>
-      <c r="N28" s="18"/>
-      <c r="O28" s="19"/>
-      <c r="P28" s="18"/>
-      <c r="Q28" s="18"/>
-      <c r="R28" s="18"/>
-      <c r="S28" s="19"/>
-      <c r="T28" s="18"/>
-      <c r="U28" s="18"/>
+        <v>1</v>
+      </c>
+      <c r="L28" s="18">
+        <v>0.01</v>
+      </c>
+      <c r="M28" s="18">
+        <v>0.01</v>
+      </c>
+      <c r="N28" s="18">
+        <v>0.01</v>
+      </c>
+      <c r="O28" s="18">
+        <v>0.01</v>
+      </c>
+      <c r="P28" s="18">
+        <v>0.01</v>
+      </c>
+      <c r="Q28" s="18">
+        <v>0.01</v>
+      </c>
+      <c r="R28" s="18">
+        <v>0.01</v>
+      </c>
+      <c r="S28" s="18">
+        <v>0.01</v>
+      </c>
+      <c r="T28" s="18">
+        <v>0.01</v>
+      </c>
+      <c r="U28" s="18">
+        <v>0.01</v>
+      </c>
       <c r="V28" s="18"/>
-      <c r="W28" s="19">
-        <v>0.5</v>
-      </c>
+      <c r="W28" s="19"/>
       <c r="X28" s="20"/>
       <c r="Y28" s="20"/>
       <c r="Z28" s="20"/>
@@ -12476,49 +12492,49 @@
       <c r="AJ28" s="20"/>
       <c r="AK28" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.5</v>
+        <v>9.9999999999999992E-2</v>
       </c>
       <c r="AL28" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>0.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:38">
       <c r="A29" s="4" t="s">
-        <v>40</v>
+        <v>234</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>41</v>
+        <v>235</v>
       </c>
       <c r="C29" s="11" t="s">
         <v>5</v>
       </c>
       <c r="D29" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E29" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
       <c r="F29" s="11" t="s">
-        <v>377</v>
+        <v>343</v>
       </c>
       <c r="G29" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="I29" s="11">
         <v>3</v>
       </c>
       <c r="J29" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K29" s="11">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="L29" s="18"/>
       <c r="M29" s="18"/>
@@ -12526,13 +12542,15 @@
       <c r="O29" s="19"/>
       <c r="P29" s="18"/>
       <c r="Q29" s="18"/>
-      <c r="R29" s="18"/>
+      <c r="R29" s="18">
+        <v>0.2</v>
+      </c>
       <c r="S29" s="19"/>
-      <c r="T29" s="18">
-        <v>-0.2</v>
-      </c>
+      <c r="T29" s="18"/>
       <c r="U29" s="18"/>
-      <c r="V29" s="18"/>
+      <c r="V29" s="18">
+        <v>0.2</v>
+      </c>
       <c r="W29" s="19"/>
       <c r="X29" s="20"/>
       <c r="Y29" s="20"/>
@@ -12549,49 +12567,49 @@
       <c r="AJ29" s="20"/>
       <c r="AK29" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AL29" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:38">
-      <c r="A30" s="48" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" s="49" t="s">
-        <v>41</v>
-      </c>
-      <c r="C30" s="50" t="s">
-        <v>5</v>
-      </c>
-      <c r="D30" s="51">
+      <c r="A30" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D30" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>20</v>
-      </c>
-      <c r="E30" s="51">
+        <v>100</v>
+      </c>
+      <c r="E30" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
-      <c r="F30" s="50" t="s">
-        <v>206</v>
-      </c>
-      <c r="G30" s="50" t="s">
+      <c r="F30" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="G30" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="H30" s="50" t="s">
-        <v>304</v>
-      </c>
-      <c r="I30" s="50">
-        <v>3</v>
-      </c>
-      <c r="J30" s="50">
+      <c r="H30" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="I30" s="11">
+        <v>1</v>
+      </c>
+      <c r="J30" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>8</v>
-      </c>
-      <c r="K30" s="50">
-        <v>6</v>
+        <v>20</v>
+      </c>
+      <c r="K30" s="11">
+        <v>0.5</v>
       </c>
       <c r="L30" s="18"/>
       <c r="M30" s="18"/>
@@ -12599,14 +12617,14 @@
       <c r="O30" s="19"/>
       <c r="P30" s="18"/>
       <c r="Q30" s="18"/>
-      <c r="R30" s="18">
-        <v>0.2</v>
-      </c>
+      <c r="R30" s="18"/>
       <c r="S30" s="19"/>
       <c r="T30" s="18"/>
       <c r="U30" s="18"/>
       <c r="V30" s="18"/>
-      <c r="W30" s="19"/>
+      <c r="W30" s="19">
+        <v>0.5</v>
+      </c>
       <c r="X30" s="20"/>
       <c r="Y30" s="20"/>
       <c r="Z30" s="20"/>
@@ -12622,74 +12640,60 @@
       <c r="AJ30" s="20"/>
       <c r="AK30" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="AL30" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:38" ht="28">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:38">
       <c r="A31" s="4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>125</v>
+        <v>5</v>
       </c>
       <c r="D31" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="E31" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
-      <c r="F31" s="37" t="s">
-        <v>383</v>
+      <c r="F31" s="11" t="s">
+        <v>377</v>
       </c>
       <c r="G31" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>344</v>
+        <v>304</v>
       </c>
       <c r="I31" s="11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J31" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>0.4</v>
-      </c>
-      <c r="K31" s="11"/>
-      <c r="L31" s="18">
-        <v>0.01</v>
-      </c>
-      <c r="M31" s="18">
-        <v>0.01</v>
-      </c>
-      <c r="N31" s="18">
-        <v>0.01</v>
-      </c>
-      <c r="O31" s="18">
-        <v>0.01</v>
-      </c>
-      <c r="P31" s="18">
-        <v>0.01</v>
-      </c>
-      <c r="Q31" s="18">
-        <v>0.01</v>
-      </c>
-      <c r="R31" s="18">
-        <v>0.01</v>
-      </c>
-      <c r="S31" s="18">
-        <v>0.01</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K31" s="11">
+        <v>6</v>
+      </c>
+      <c r="L31" s="18"/>
+      <c r="M31" s="18"/>
+      <c r="N31" s="18"/>
+      <c r="O31" s="19"/>
+      <c r="P31" s="18"/>
+      <c r="Q31" s="18"/>
+      <c r="R31" s="18"/>
+      <c r="S31" s="19"/>
       <c r="T31" s="18">
-        <v>0.01</v>
+        <v>-0.2</v>
       </c>
       <c r="U31" s="18"/>
       <c r="V31" s="18"/>
@@ -12709,65 +12713,61 @@
       <c r="AJ31" s="20"/>
       <c r="AK31" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="AL31" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>3.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:38">
-      <c r="A32" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C32" s="11" t="s">
+      <c r="A32" s="48" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" s="49" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="D32" s="29">
+      <c r="D32" s="51">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>100</v>
-      </c>
-      <c r="E32" s="29">
+        <v>20</v>
+      </c>
+      <c r="E32" s="51">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
-      <c r="F32" s="11" t="s">
-        <v>382</v>
-      </c>
-      <c r="G32" s="11" t="s">
+      <c r="F32" s="50" t="s">
+        <v>206</v>
+      </c>
+      <c r="G32" s="50" t="s">
         <v>229</v>
       </c>
-      <c r="H32" s="11" t="s">
-        <v>298</v>
-      </c>
-      <c r="I32" s="11">
-        <v>2</v>
-      </c>
-      <c r="J32" s="11">
+      <c r="H32" s="50" t="s">
+        <v>304</v>
+      </c>
+      <c r="I32" s="50">
+        <v>3</v>
+      </c>
+      <c r="J32" s="50">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>3.2</v>
-      </c>
-      <c r="K32" s="11">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="K32" s="50">
+        <v>6</v>
       </c>
       <c r="L32" s="18"/>
       <c r="M32" s="18"/>
       <c r="N32" s="18"/>
-      <c r="O32" s="19">
-        <v>0.08</v>
-      </c>
-      <c r="P32" s="19"/>
+      <c r="O32" s="19"/>
+      <c r="P32" s="18"/>
       <c r="Q32" s="18"/>
-      <c r="R32" s="18"/>
-      <c r="S32" s="18">
-        <v>-7.4999999999999997E-2</v>
-      </c>
-      <c r="T32" s="18">
-        <v>0.08</v>
-      </c>
+      <c r="R32" s="18">
+        <v>0.2</v>
+      </c>
+      <c r="S32" s="19"/>
+      <c r="T32" s="18"/>
       <c r="U32" s="18"/>
       <c r="V32" s="18"/>
       <c r="W32" s="19"/>
@@ -12786,14 +12786,14 @@
       <c r="AJ32" s="20"/>
       <c r="AK32" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="AL32" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:38">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:38" ht="27">
       <c r="A33" s="4" t="s">
         <v>44</v>
       </c>
@@ -12801,7 +12801,7 @@
         <v>42</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D33" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
@@ -12811,38 +12811,50 @@
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
-      <c r="F33" s="11" t="s">
-        <v>208</v>
+      <c r="F33" s="37" t="s">
+        <v>383</v>
       </c>
       <c r="G33" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>298</v>
+        <v>344</v>
       </c>
       <c r="I33" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J33" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>8</v>
-      </c>
-      <c r="K33" s="11">
-        <v>15</v>
-      </c>
-      <c r="L33" s="18"/>
-      <c r="M33" s="18"/>
-      <c r="N33" s="18"/>
-      <c r="O33" s="19"/>
-      <c r="P33" s="18"/>
-      <c r="Q33" s="18"/>
+        <v>0.4</v>
+      </c>
+      <c r="K33" s="11"/>
+      <c r="L33" s="18">
+        <v>0.01</v>
+      </c>
+      <c r="M33" s="18">
+        <v>0.01</v>
+      </c>
+      <c r="N33" s="18">
+        <v>0.01</v>
+      </c>
+      <c r="O33" s="18">
+        <v>0.01</v>
+      </c>
+      <c r="P33" s="18">
+        <v>0.01</v>
+      </c>
+      <c r="Q33" s="18">
+        <v>0.01</v>
+      </c>
       <c r="R33" s="18">
-        <v>-0.2</v>
-      </c>
-      <c r="S33" s="19">
-        <v>0.2</v>
-      </c>
-      <c r="T33" s="18"/>
+        <v>0.01</v>
+      </c>
+      <c r="S33" s="18">
+        <v>0.01</v>
+      </c>
+      <c r="T33" s="18">
+        <v>0.01</v>
+      </c>
       <c r="U33" s="18"/>
       <c r="V33" s="18"/>
       <c r="W33" s="19"/>
@@ -12861,11 +12873,11 @@
       <c r="AJ33" s="20"/>
       <c r="AK33" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
       <c r="AL33" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>15</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="34" spans="1:38">
@@ -12876,7 +12888,7 @@
         <v>42</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>122</v>
+        <v>5</v>
       </c>
       <c r="D34" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
@@ -12887,7 +12899,7 @@
         <v>10</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="G34" s="11" t="s">
         <v>229</v>
@@ -12896,29 +12908,33 @@
         <v>298</v>
       </c>
       <c r="I34" s="11">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J34" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>22</v>
+        <v>3.2</v>
       </c>
       <c r="K34" s="11">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L34" s="18"/>
       <c r="M34" s="18"/>
       <c r="N34" s="18"/>
-      <c r="O34" s="19"/>
-      <c r="P34" s="18"/>
+      <c r="O34" s="19">
+        <v>0.08</v>
+      </c>
+      <c r="P34" s="19"/>
       <c r="Q34" s="18"/>
       <c r="R34" s="18"/>
-      <c r="S34" s="19"/>
-      <c r="T34" s="18"/>
+      <c r="S34" s="18">
+        <v>-7.4999999999999997E-2</v>
+      </c>
+      <c r="T34" s="18">
+        <v>0.08</v>
+      </c>
       <c r="U34" s="18"/>
       <c r="V34" s="18"/>
-      <c r="W34" s="19">
-        <v>0.55000000000000004</v>
-      </c>
+      <c r="W34" s="19"/>
       <c r="X34" s="20"/>
       <c r="Y34" s="20"/>
       <c r="Z34" s="20"/>
@@ -12934,75 +12950,65 @@
       <c r="AJ34" s="20"/>
       <c r="AK34" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.55000000000000004</v>
+        <v>0.16</v>
       </c>
       <c r="AL34" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:38">
       <c r="A35" s="4" t="s">
-        <v>258</v>
+        <v>44</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>257</v>
+        <v>42</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>5</v>
+        <v>121</v>
       </c>
       <c r="D35" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="E35" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
       <c r="F35" s="11" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="G35" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="I35" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J35" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>2.6666666666666665</v>
-      </c>
-      <c r="K35" s="11"/>
+        <v>8</v>
+      </c>
+      <c r="K35" s="11">
+        <v>15</v>
+      </c>
       <c r="L35" s="18"/>
       <c r="M35" s="18"/>
-      <c r="N35" s="18">
-        <v>0.06</v>
-      </c>
-      <c r="O35" s="18">
-        <v>-3.5000000000000003E-2</v>
-      </c>
-      <c r="P35" s="18">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="Q35" s="18">
-        <v>-0.05</v>
-      </c>
+      <c r="N35" s="18"/>
+      <c r="O35" s="19"/>
+      <c r="P35" s="18"/>
+      <c r="Q35" s="18"/>
       <c r="R35" s="18">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="S35" s="18">
-        <v>-0.03</v>
+        <v>-0.2</v>
+      </c>
+      <c r="S35" s="19">
+        <v>0.2</v>
       </c>
       <c r="T35" s="18"/>
-      <c r="U35" s="18">
-        <v>-2.5000000000000001E-2</v>
-      </c>
-      <c r="V35" s="18">
-        <v>-2.5000000000000001E-2</v>
-      </c>
+      <c r="U35" s="18"/>
+      <c r="V35" s="18"/>
       <c r="W35" s="19"/>
       <c r="X35" s="20"/>
       <c r="Y35" s="20"/>
@@ -13023,45 +13029,45 @@
       </c>
       <c r="AL35" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:38">
       <c r="A36" s="4" t="s">
-        <v>258</v>
+        <v>44</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>257</v>
+        <v>42</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D36" s="29">
         <f>INDEX(Table2[CA weight],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="E36" s="29">
         <f>INDEX(Table2[Credits],MATCH(Table1[[#This Row],[Module Code]],Table2[Module Code],0))</f>
         <v>10</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>263</v>
+        <v>384</v>
       </c>
       <c r="G36" s="11" t="s">
         <v>229</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>320</v>
+        <v>298</v>
       </c>
       <c r="I36" s="11">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J36" s="11">
         <f>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</f>
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="K36" s="11">
-        <v>0.5</v>
+        <v>9</v>
       </c>
       <c r="L36" s="18"/>
       <c r="M36" s="18"/>
@@ -13071,12 +13077,12 @@
       <c r="Q36" s="18"/>
       <c r="R36" s="18"/>
       <c r="S36" s="19"/>
-      <c r="T36" s="18">
-        <v>0.2</v>
-      </c>
+      <c r="T36" s="18"/>
       <c r="U36" s="18"/>
       <c r="V36" s="18"/>
-      <c r="W36" s="19"/>
+      <c r="W36" s="19">
+        <v>0.55000000000000004</v>
+      </c>
       <c r="X36" s="20"/>
       <c r="Y36" s="20"/>
       <c r="Z36" s="20"/>
@@ -13092,11 +13098,11 @@
       <c r="AJ36" s="20"/>
       <c r="AK36" s="27">
         <f>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>0.2</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="AL36" s="27">
         <f>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</f>
-        <v>0.5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:38" ht="14.65" customHeight="1">
@@ -13324,7 +13330,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:38" ht="28">
+    <row r="40" spans="1:38" ht="27">
       <c r="A40" s="4" t="s">
         <v>49</v>
       </c>
@@ -14815,7 +14821,7 @@
         <v>12.000000000000004</v>
       </c>
     </row>
-    <row r="59" spans="1:38" ht="28">
+    <row r="59" spans="1:38" ht="27">
       <c r="A59" s="3" t="s">
         <v>186</v>
       </c>
@@ -14894,7 +14900,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:38" ht="28">
+    <row r="60" spans="1:38" ht="27">
       <c r="A60" s="3" t="s">
         <v>186</v>
       </c>
@@ -15808,7 +15814,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="72" spans="1:38" ht="28">
+    <row r="72" spans="1:38" ht="27">
       <c r="A72" s="4" t="s">
         <v>1</v>
       </c>
@@ -17197,7 +17203,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="90" spans="1:38" ht="28">
+    <row r="90" spans="1:38" ht="27">
       <c r="A90" s="4" t="s">
         <v>18</v>
       </c>
@@ -17276,7 +17282,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="91" spans="1:38" ht="28">
+    <row r="91" spans="1:38" ht="27">
       <c r="A91" s="4" t="s">
         <v>18</v>
       </c>
@@ -17870,7 +17876,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="99" spans="1:38" ht="28">
+    <row r="99" spans="1:38" ht="27">
       <c r="A99" s="3" t="s">
         <v>106</v>
       </c>
@@ -18160,7 +18166,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="103" spans="1:38" ht="28">
+    <row r="103" spans="1:38" ht="27">
       <c r="A103" s="3" t="s">
         <v>108</v>
       </c>
@@ -19300,7 +19306,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="118" spans="1:38" ht="28">
+    <row r="118" spans="1:38" ht="27">
       <c r="A118" s="4" t="s">
         <v>61</v>
       </c>
@@ -19675,7 +19681,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="123" spans="1:38" ht="28">
+    <row r="123" spans="1:38" ht="27">
       <c r="A123" s="4" t="s">
         <v>63</v>
       </c>
@@ -19748,7 +19754,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="124" spans="1:38" ht="28">
+    <row r="124" spans="1:38" ht="27">
       <c r="A124" s="4" t="s">
         <v>66</v>
       </c>
@@ -20219,7 +20225,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="130" spans="1:38" ht="28">
+    <row r="130" spans="1:38" ht="27">
       <c r="A130" s="4" t="s">
         <v>71</v>
       </c>
@@ -20529,7 +20535,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="134" spans="1:38" ht="28">
+    <row r="134" spans="1:38" ht="27">
       <c r="A134" s="3" t="s">
         <v>192</v>
       </c>
@@ -20762,7 +20768,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="137" spans="1:38" ht="28">
+    <row r="137" spans="1:38" ht="27">
       <c r="A137" s="3" t="s">
         <v>193</v>
       </c>
@@ -20843,7 +20849,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="138" spans="1:38" ht="28">
+    <row r="138" spans="1:38" ht="27">
       <c r="A138" s="3" t="s">
         <v>193</v>
       </c>
@@ -21139,7 +21145,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="142" spans="1:38" ht="28">
+    <row r="142" spans="1:38" ht="27">
       <c r="A142" s="3" t="s">
         <v>239</v>
       </c>
@@ -21307,7 +21313,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="144" spans="1:38" ht="28">
+    <row r="144" spans="1:38" ht="27">
       <c r="A144" s="3" t="s">
         <v>116</v>
       </c>
@@ -21386,7 +21392,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="145" spans="1:38" ht="28">
+    <row r="145" spans="1:38" ht="27">
       <c r="A145" s="3" t="s">
         <v>116</v>
       </c>
@@ -24441,16 +24447,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0482654D-1732-43E5-85EC-021407B07CE5}">
   <dimension ref="A1:AE141"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14.81640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="50.81640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.796875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.796875" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="10" style="10" customWidth="1"/>
-    <col min="6" max="6" width="10.7265625" style="10" customWidth="1"/>
-    <col min="7" max="15" width="16.26953125" style="14" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="17.26953125" style="14" bestFit="1" customWidth="1"/>
-    <col min="19" max="30" width="8.7265625" style="16"/>
+    <col min="6" max="6" width="10.73046875" style="10" customWidth="1"/>
+    <col min="7" max="15" width="16.265625" style="14" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="17.265625" style="14" bestFit="1" customWidth="1"/>
+    <col min="19" max="30" width="8.73046875" style="16"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31">
@@ -30591,14 +30597,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D548CE7-BEAC-43FA-847F-FDE82E3A5926}">
   <dimension ref="A1:X132"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14.81640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="66.81640625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="16.26953125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="7.81640625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="10.7265625" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.26953125" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.796875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="66.796875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="16.265625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="7.796875" style="5" customWidth="1"/>
+    <col min="5" max="5" width="10.73046875" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.265625" style="5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="5" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="9" style="5" customWidth="1"/>
   </cols>
@@ -36394,11 +36400,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF4F541C-C22C-46EF-BD21-4F8C93ABA5A9}">
   <dimension ref="A3:F70"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="19.54296875" customWidth="1"/>
+    <col min="1" max="1" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="19.53125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:6">

--- a/AssessmentSchedule_2627_v2.xlsx
+++ b/AssessmentSchedule_2627_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cf-my.sharepoint.com/personal/northce_cardiff_ac_uk/Documents/Documents/Cardiff/DUGS/Assessments/Schedule Modelling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="235" documentId="8_{0C641013-E594-4AA6-B777-C2C249EA34A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{357115BB-E968-45F9-A82B-E04E8F53CDFD}"/>
+  <xr:revisionPtr revIDLastSave="236" documentId="8_{0C641013-E594-4AA6-B777-C2C249EA34A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0CD3019A-D30A-4168-A4CE-49D2722C1F12}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{A20BCC1C-F123-4C76-9181-B345A7D760BE}"/>
   </bookViews>
@@ -12275,7 +12275,7 @@
         <v>229</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>298</v>
+        <v>320</v>
       </c>
       <c r="I26" s="11">
         <v>2</v>

--- a/AssessmentSchedule_2627_v2.xlsx
+++ b/AssessmentSchedule_2627_v2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cf-my.sharepoint.com/personal/northce_cardiff_ac_uk/Documents/Documents/Cardiff/DUGS/Assessments/Schedule Modelling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="236" documentId="8_{0C641013-E594-4AA6-B777-C2C249EA34A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0CD3019A-D30A-4168-A4CE-49D2722C1F12}"/>
+  <xr:revisionPtr revIDLastSave="246" documentId="8_{0C641013-E594-4AA6-B777-C2C249EA34A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87B85A92-371A-4792-BC4F-26B3456616A6}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{A20BCC1C-F123-4C76-9181-B345A7D760BE}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="26116" windowHeight="15675" activeTab="2" xr2:uid="{A20BCC1C-F123-4C76-9181-B345A7D760BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Assessments" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="5" r:id="rId5"/>
+    <pivotCache cacheId="3" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -9305,7 +9305,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3F344565-A902-475D-ACD8-7DA2FB255CBD}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3F344565-A902-475D-ACD8-7DA2FB255CBD}" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:B70" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
   <pivotFields count="34">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -10218,21 +10218,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66039B40-29AD-4D93-B125-EAF72A7B3996}">
   <dimension ref="A1:AL185"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="14.796875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="50.796875" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.81640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.81640625" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="10" style="10" customWidth="1"/>
-    <col min="6" max="6" width="21.73046875" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="21.73046875" style="10" customWidth="1"/>
-    <col min="9" max="9" width="10.73046875" style="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="10.73046875" style="10" customWidth="1"/>
-    <col min="12" max="23" width="9.19921875" style="14" customWidth="1"/>
-    <col min="24" max="36" width="9.19921875" style="16" customWidth="1"/>
+    <col min="6" max="6" width="21.7265625" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="21.7265625" style="10" customWidth="1"/>
+    <col min="9" max="9" width="10.7265625" style="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="10.7265625" style="10" customWidth="1"/>
+    <col min="12" max="23" width="9.1796875" style="14" customWidth="1"/>
+    <col min="24" max="36" width="9.1796875" style="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" s="44" customFormat="1" ht="28.5">
+    <row r="1" spans="1:38" s="44" customFormat="1" ht="29">
       <c r="A1" s="39" t="s">
         <v>0</v>
       </c>
@@ -10646,7 +10646,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:38" ht="27">
+    <row r="6" spans="1:38" ht="28">
       <c r="A6" s="4" t="s">
         <v>252</v>
       </c>
@@ -11227,7 +11227,7 @@
         <v>29.6</v>
       </c>
     </row>
-    <row r="13" spans="1:38" ht="27">
+    <row r="13" spans="1:38" ht="28">
       <c r="A13" s="3" t="s">
         <v>81</v>
       </c>
@@ -12003,7 +12003,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:38" ht="27">
+    <row r="23" spans="1:38" ht="28">
       <c r="A23" s="4" t="s">
         <v>37</v>
       </c>
@@ -12793,7 +12793,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:38" ht="27">
+    <row r="33" spans="1:38" ht="28">
       <c r="A33" s="4" t="s">
         <v>44</v>
       </c>
@@ -13330,7 +13330,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:38" ht="27">
+    <row r="40" spans="1:38" ht="28">
       <c r="A40" s="4" t="s">
         <v>49</v>
       </c>
@@ -14821,7 +14821,7 @@
         <v>12.000000000000004</v>
       </c>
     </row>
-    <row r="59" spans="1:38" ht="27">
+    <row r="59" spans="1:38" ht="28">
       <c r="A59" s="3" t="s">
         <v>186</v>
       </c>
@@ -14900,7 +14900,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:38" ht="27">
+    <row r="60" spans="1:38" ht="28">
       <c r="A60" s="3" t="s">
         <v>186</v>
       </c>
@@ -15814,7 +15814,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="72" spans="1:38" ht="27">
+    <row r="72" spans="1:38" ht="28">
       <c r="A72" s="4" t="s">
         <v>1</v>
       </c>
@@ -17203,7 +17203,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="90" spans="1:38" ht="27">
+    <row r="90" spans="1:38" ht="28">
       <c r="A90" s="4" t="s">
         <v>18</v>
       </c>
@@ -17282,7 +17282,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="91" spans="1:38" ht="27">
+    <row r="91" spans="1:38" ht="28">
       <c r="A91" s="4" t="s">
         <v>18</v>
       </c>
@@ -17876,7 +17876,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="99" spans="1:38" ht="27">
+    <row r="99" spans="1:38" ht="28">
       <c r="A99" s="3" t="s">
         <v>106</v>
       </c>
@@ -18166,7 +18166,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="103" spans="1:38" ht="27">
+    <row r="103" spans="1:38" ht="28">
       <c r="A103" s="3" t="s">
         <v>108</v>
       </c>
@@ -19306,7 +19306,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="118" spans="1:38" ht="27">
+    <row r="118" spans="1:38" ht="28">
       <c r="A118" s="4" t="s">
         <v>61</v>
       </c>
@@ -19681,7 +19681,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="123" spans="1:38" ht="27">
+    <row r="123" spans="1:38" ht="28">
       <c r="A123" s="4" t="s">
         <v>63</v>
       </c>
@@ -19754,7 +19754,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="124" spans="1:38" ht="27">
+    <row r="124" spans="1:38" ht="28">
       <c r="A124" s="4" t="s">
         <v>66</v>
       </c>
@@ -20225,7 +20225,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="130" spans="1:38" ht="27">
+    <row r="130" spans="1:38" ht="28">
       <c r="A130" s="4" t="s">
         <v>71</v>
       </c>
@@ -20535,7 +20535,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="134" spans="1:38" ht="27">
+    <row r="134" spans="1:38" ht="28">
       <c r="A134" s="3" t="s">
         <v>192</v>
       </c>
@@ -20768,7 +20768,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="137" spans="1:38" ht="27">
+    <row r="137" spans="1:38" ht="28">
       <c r="A137" s="3" t="s">
         <v>193</v>
       </c>
@@ -20849,7 +20849,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="138" spans="1:38" ht="27">
+    <row r="138" spans="1:38" ht="28">
       <c r="A138" s="3" t="s">
         <v>193</v>
       </c>
@@ -21145,7 +21145,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="142" spans="1:38" ht="27">
+    <row r="142" spans="1:38" ht="28">
       <c r="A142" s="3" t="s">
         <v>239</v>
       </c>
@@ -21313,7 +21313,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="144" spans="1:38" ht="27">
+    <row r="144" spans="1:38" ht="28">
       <c r="A144" s="3" t="s">
         <v>116</v>
       </c>
@@ -21392,7 +21392,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="145" spans="1:38" ht="27">
+    <row r="145" spans="1:38" ht="28">
       <c r="A145" s="3" t="s">
         <v>116</v>
       </c>
@@ -24447,16 +24447,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0482654D-1732-43E5-85EC-021407B07CE5}">
   <dimension ref="A1:AE141"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="14.796875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="50.796875" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.81640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="50.81640625" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" style="10" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="10" style="10" customWidth="1"/>
-    <col min="6" max="6" width="10.73046875" style="10" customWidth="1"/>
-    <col min="7" max="15" width="16.265625" style="14" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="17.265625" style="14" bestFit="1" customWidth="1"/>
-    <col min="19" max="30" width="8.73046875" style="16"/>
+    <col min="6" max="6" width="10.7265625" style="10" customWidth="1"/>
+    <col min="7" max="15" width="16.26953125" style="14" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="17.26953125" style="14" bestFit="1" customWidth="1"/>
+    <col min="19" max="30" width="8.7265625" style="16"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31">
@@ -30597,14 +30597,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D548CE7-BEAC-43FA-847F-FDE82E3A5926}">
   <dimension ref="A1:X132"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="14.796875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="66.796875" style="5" customWidth="1"/>
-    <col min="3" max="3" width="16.265625" style="5" customWidth="1"/>
-    <col min="4" max="4" width="7.796875" style="5" customWidth="1"/>
-    <col min="5" max="5" width="10.73046875" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.265625" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.81640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="66.81640625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="16.26953125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="7.81640625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="10.7265625" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.26953125" style="5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="5" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="9" style="5" customWidth="1"/>
   </cols>
@@ -33005,6 +33005,12 @@
       <c r="L46" t="s">
         <v>143</v>
       </c>
+      <c r="U46">
+        <v>0.5</v>
+      </c>
+      <c r="V46">
+        <v>0</v>
+      </c>
       <c r="W46">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
         <v>100</v>
@@ -33040,6 +33046,12 @@
       <c r="I47" s="28"/>
       <c r="M47" t="s">
         <v>143</v>
+      </c>
+      <c r="U47">
+        <v>0.5</v>
+      </c>
+      <c r="V47">
+        <v>0</v>
       </c>
       <c r="W47">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
@@ -34052,10 +34064,15 @@
       <c r="R65" s="6"/>
       <c r="S65" s="6"/>
       <c r="T65" s="6"/>
-      <c r="U65" s="6"/>
+      <c r="U65" s="6">
+        <v>0.5</v>
+      </c>
+      <c r="V65">
+        <v>25</v>
+      </c>
       <c r="W65">
         <f>100-Table2[[#This Row],[Exam Weight (%)]]</f>
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="X65">
         <f>IF(COUNTIF(Table1[Module Code],Table2[[#This Row],[Module Code]])&gt;0,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Module Code]],Table1[Summative],"Y")*100,SUMIFS(Table1[Sub-total],Table1[Module Code],Table2[[#This Row],[Alternative Module Code]],Table1[Summative],"Y")*100)</f>
@@ -36400,11 +36417,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF4F541C-C22C-46EF-BD21-4F8C93ABA5A9}">
   <dimension ref="A3:F70"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.46484375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="19.53125" customWidth="1"/>
+    <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="19.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:6">

--- a/AssessmentSchedule_2627_v2.xlsx
+++ b/AssessmentSchedule_2627_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cf-my.sharepoint.com/personal/northce_cardiff_ac_uk/Documents/Documents/Cardiff/DUGS/Assessments/Schedule Modelling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="246" documentId="8_{0C641013-E594-4AA6-B777-C2C249EA34A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87B85A92-371A-4792-BC4F-26B3456616A6}"/>
+  <xr:revisionPtr revIDLastSave="248" documentId="8_{0C641013-E594-4AA6-B777-C2C249EA34A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2422B9DF-796A-46F0-B2F2-91CCAA23F76D}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="26116" windowHeight="15675" activeTab="2" xr2:uid="{A20BCC1C-F123-4C76-9181-B345A7D760BE}"/>
   </bookViews>

--- a/AssessmentSchedule_2627_v2.xlsx
+++ b/AssessmentSchedule_2627_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cf-my.sharepoint.com/personal/northce_cardiff_ac_uk/Documents/Documents/Cardiff/DUGS/Assessments/Schedule Modelling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="248" documentId="8_{0C641013-E594-4AA6-B777-C2C249EA34A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2422B9DF-796A-46F0-B2F2-91CCAA23F76D}"/>
+  <xr:revisionPtr revIDLastSave="249" documentId="8_{0C641013-E594-4AA6-B777-C2C249EA34A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FBA324E-4652-42BF-A934-EF70E5B8E75B}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="26116" windowHeight="15675" activeTab="2" xr2:uid="{A20BCC1C-F123-4C76-9181-B345A7D760BE}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="26116" windowHeight="15675" activeTab="1" xr2:uid="{A20BCC1C-F123-4C76-9181-B345A7D760BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Assessments" sheetId="1" r:id="rId1"/>
@@ -30175,7 +30175,7 @@
         <v>0.5</v>
       </c>
       <c r="G61" s="31">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="H61" s="31">
         <v>1</v>
@@ -30246,7 +30246,7 @@
       </c>
       <c r="AE61" s="37">
         <f>SUM(Table14[[#This Row],[Autumn Week 1]:[Spring Week 12]])</f>
-        <v>29.5</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="62" spans="1:31">
@@ -37969,15 +37969,15 @@
       </c>
       <c r="D67">
         <f>INDEX(Table14[Total],MATCH(Sheet2!A67,Table14[Module Code],0))</f>
-        <v>29.5</v>
+        <v>12.5</v>
       </c>
       <c r="E67">
         <f t="shared" si="0"/>
-        <v>530.90000000000009</v>
+        <v>513.90000000000009</v>
       </c>
       <c r="F67">
         <f t="shared" si="1"/>
-        <v>8.8483333333333345</v>
+        <v>8.5650000000000013</v>
       </c>
     </row>
     <row r="68" spans="1:6">

--- a/AssessmentSchedule_2627_v2.xlsx
+++ b/AssessmentSchedule_2627_v2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cf-my.sharepoint.com/personal/northce_cardiff_ac_uk/Documents/Documents/Cardiff/DUGS/Assessments/Schedule Modelling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="249" documentId="8_{0C641013-E594-4AA6-B777-C2C249EA34A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FBA324E-4652-42BF-A934-EF70E5B8E75B}"/>
+  <xr:revisionPtr revIDLastSave="253" documentId="8_{0C641013-E594-4AA6-B777-C2C249EA34A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B5FB604-0A9C-46C5-B914-FDF971277748}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="26116" windowHeight="15675" activeTab="1" xr2:uid="{A20BCC1C-F123-4C76-9181-B345A7D760BE}"/>
+    <workbookView xWindow="1590" yWindow="1660" windowWidth="28800" windowHeight="15360" xr2:uid="{A20BCC1C-F123-4C76-9181-B345A7D760BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Assessments" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId5"/>
+    <pivotCache cacheId="6" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -2020,861 +2020,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor rgb="FF000000"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri (Body)"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor rgb="FF000000"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color auto="1"/>
@@ -3905,6 +3050,861 @@
         <bottom/>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor rgb="FF000000"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri (Body)"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor rgb="FF000000"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -9305,7 +9305,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3F344565-A902-475D-ACD8-7DA2FB255CBD}" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3F344565-A902-475D-ACD8-7DA2FB255CBD}" name="PivotTable1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:B70" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
   <pivotFields count="34">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
@@ -9754,54 +9754,54 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FA69A777-C149-48BD-B248-35F32F0AC920}" name="Table1" displayName="Table1" ref="A1:AL185" totalsRowShown="0" headerRowDxfId="116" dataDxfId="114" headerRowBorderDxfId="115" tableBorderDxfId="113" totalsRowBorderDxfId="112">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FA69A777-C149-48BD-B248-35F32F0AC920}" name="Table1" displayName="Table1" ref="A1:AL185" totalsRowShown="0" headerRowDxfId="80" dataDxfId="78" headerRowBorderDxfId="79" tableBorderDxfId="77" totalsRowBorderDxfId="76">
   <autoFilter ref="A1:AL185" xr:uid="{FA69A777-C149-48BD-B248-35F32F0AC920}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AI156">
     <sortCondition ref="A1:A156"/>
   </sortState>
   <tableColumns count="38">
-    <tableColumn id="1" xr3:uid="{7078548A-F011-4851-AB36-1F04238FA2FE}" name="Module Code" dataDxfId="111"/>
-    <tableColumn id="2" xr3:uid="{D2290F36-B8B3-427A-AEFE-45FD22901411}" name="Module Title" dataDxfId="110"/>
-    <tableColumn id="3" xr3:uid="{31165455-2AA3-4532-A0A0-C942837C0F79}" name="CA type" dataDxfId="109"/>
-    <tableColumn id="33" xr3:uid="{B83E0E3E-2B28-42F1-BC64-5D7177EC4229}" name="CA Weight" dataDxfId="108"/>
-    <tableColumn id="34" xr3:uid="{AEA2048C-138D-450A-BE52-3FCBDE03C67D}" name="Credits" dataDxfId="107"/>
-    <tableColumn id="30" xr3:uid="{82DD5B5B-C808-4E6E-849C-7A03DC6D0B69}" name="Description" dataDxfId="106"/>
-    <tableColumn id="36" xr3:uid="{A7BF30F6-C808-4B8F-B3FF-9FAF20E2145A}" name="Summative" dataDxfId="105"/>
-    <tableColumn id="37" xr3:uid="{68E504F9-116C-43AB-BCC6-3BB48B0860D2}" name="Day of Week" dataDxfId="104"/>
-    <tableColumn id="16" xr3:uid="{E6637FEB-7F23-45F0-99D2-96D20DD2DAEF}" name="Duration" dataDxfId="103"/>
-    <tableColumn id="31" xr3:uid="{FD1E9614-3960-4F72-BD42-711A4CC7BBA0}" name="Nominal Hours" dataDxfId="102">
+    <tableColumn id="1" xr3:uid="{7078548A-F011-4851-AB36-1F04238FA2FE}" name="Module Code" dataDxfId="75"/>
+    <tableColumn id="2" xr3:uid="{D2290F36-B8B3-427A-AEFE-45FD22901411}" name="Module Title" dataDxfId="74"/>
+    <tableColumn id="3" xr3:uid="{31165455-2AA3-4532-A0A0-C942837C0F79}" name="CA type" dataDxfId="73"/>
+    <tableColumn id="33" xr3:uid="{B83E0E3E-2B28-42F1-BC64-5D7177EC4229}" name="CA Weight" dataDxfId="72"/>
+    <tableColumn id="34" xr3:uid="{AEA2048C-138D-450A-BE52-3FCBDE03C67D}" name="Credits" dataDxfId="71"/>
+    <tableColumn id="30" xr3:uid="{82DD5B5B-C808-4E6E-849C-7A03DC6D0B69}" name="Description" dataDxfId="70"/>
+    <tableColumn id="36" xr3:uid="{A7BF30F6-C808-4B8F-B3FF-9FAF20E2145A}" name="Summative" dataDxfId="69"/>
+    <tableColumn id="37" xr3:uid="{68E504F9-116C-43AB-BCC6-3BB48B0860D2}" name="Day of Week" dataDxfId="68"/>
+    <tableColumn id="16" xr3:uid="{E6637FEB-7F23-45F0-99D2-96D20DD2DAEF}" name="Duration" dataDxfId="67"/>
+    <tableColumn id="31" xr3:uid="{FD1E9614-3960-4F72-BD42-711A4CC7BBA0}" name="Nominal Hours" dataDxfId="66">
       <calculatedColumnFormula>IFERROR(AVERAGEIF(Table1[[#This Row],[Autumn Week 1]:[Spring Exams]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Exams]])*4*Table1[[#This Row],[Credits]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="32" xr3:uid="{E11C773A-511F-4D25-8636-C56C5B61ED90}" name="Hours" dataDxfId="101"/>
-    <tableColumn id="4" xr3:uid="{04E38F13-8347-412C-866C-6EFE6796253C}" name="Autumn Week 1" dataDxfId="100"/>
-    <tableColumn id="5" xr3:uid="{254D6A24-FC1B-44C7-A3DF-52DA2A250D31}" name="Autumn Week 2" dataDxfId="99"/>
-    <tableColumn id="6" xr3:uid="{9EB326C3-772E-4E56-89FB-BA3A00291293}" name="Autumn Week 3" dataDxfId="98"/>
-    <tableColumn id="7" xr3:uid="{94BC6C78-5A89-4267-B1C1-BFA70E5A9F34}" name="Autumn Week 4" dataDxfId="97"/>
-    <tableColumn id="8" xr3:uid="{CF3B6389-B559-4FE3-8B33-FEDB303382B1}" name="Autumn Week 5" dataDxfId="96"/>
-    <tableColumn id="9" xr3:uid="{8DD80B9C-D1B1-4CDE-A624-4CD3A15113DD}" name="Autumn Week 6" dataDxfId="95"/>
-    <tableColumn id="10" xr3:uid="{8C4EBEE4-01CB-4AD0-B594-F466CC36D370}" name="Autumn Week 7" dataDxfId="94"/>
-    <tableColumn id="11" xr3:uid="{7F8C91DE-BE61-47CF-A916-D06ED7B283E9}" name="Autumn Week 8" dataDxfId="93"/>
-    <tableColumn id="12" xr3:uid="{9D58139A-0F96-4203-8D22-58BC34744B87}" name="Autumn Week 9" dataDxfId="92"/>
-    <tableColumn id="13" xr3:uid="{43C545DF-9B9E-4080-8012-F9EFA0F01283}" name="Autumn Week 10" dataDxfId="91"/>
-    <tableColumn id="14" xr3:uid="{829AB976-2AB2-435C-8F11-DE08DACA4407}" name="Autumn Week 11" dataDxfId="90"/>
-    <tableColumn id="15" xr3:uid="{9126A0EA-FC34-4876-9D56-A0AC39C5526C}" name="Autumn Week 12" dataDxfId="89"/>
-    <tableColumn id="17" xr3:uid="{15B891EE-FCC8-4E53-A90D-3E10FFC1E9FA}" name="Spring Week 1" dataDxfId="88"/>
-    <tableColumn id="18" xr3:uid="{464CA212-3B53-4678-AFE4-8AF8308C1986}" name="Spring Week 2" dataDxfId="87"/>
-    <tableColumn id="19" xr3:uid="{B560E823-CC29-418C-B26C-52D9FFC8C72E}" name="Spring Week 3" dataDxfId="86"/>
-    <tableColumn id="20" xr3:uid="{D95606F3-E0A0-4907-91E0-4AD09D0C65CB}" name="Spring Week 4" dataDxfId="85"/>
-    <tableColumn id="21" xr3:uid="{E71FF892-9A4B-444C-8972-62D92F81B0E7}" name="Spring Week 5" dataDxfId="84"/>
-    <tableColumn id="22" xr3:uid="{C7775BA8-178A-4501-A8DE-2B2CF77A2451}" name="Spring Week 6" dataDxfId="83"/>
-    <tableColumn id="23" xr3:uid="{51A89A97-F839-4F50-88A9-65049D65C9B0}" name="Spring Week 7" dataDxfId="82"/>
-    <tableColumn id="24" xr3:uid="{26EE6D10-4FC4-49AE-8DE6-18AC556C293D}" name="Spring Week 8" dataDxfId="81"/>
-    <tableColumn id="25" xr3:uid="{FCB1B9FB-21DA-415A-86E6-C8E14F864E1B}" name="Spring Week 9" dataDxfId="80"/>
-    <tableColumn id="26" xr3:uid="{54402AE1-DC77-41BA-BCC7-28BCA7186B44}" name="Spring Week 10" dataDxfId="79"/>
-    <tableColumn id="27" xr3:uid="{31C092D1-BD77-4126-8E72-8E74D0D11509}" name="Spring Week 11" dataDxfId="78"/>
-    <tableColumn id="28" xr3:uid="{56D67770-E36A-46FE-97FA-76CD24229C51}" name="Spring Week 12" dataDxfId="77"/>
-    <tableColumn id="38" xr3:uid="{29E08DCE-0D92-40C5-8F33-F1B96FB2F7A4}" name="Spring Exams" dataDxfId="76"/>
-    <tableColumn id="29" xr3:uid="{785AD842-5ED0-4E27-B4B7-26E6FF9AC266}" name="Sub-total" dataDxfId="75">
+    <tableColumn id="32" xr3:uid="{E11C773A-511F-4D25-8636-C56C5B61ED90}" name="Hours" dataDxfId="65"/>
+    <tableColumn id="4" xr3:uid="{04E38F13-8347-412C-866C-6EFE6796253C}" name="Autumn Week 1" dataDxfId="64"/>
+    <tableColumn id="5" xr3:uid="{254D6A24-FC1B-44C7-A3DF-52DA2A250D31}" name="Autumn Week 2" dataDxfId="63"/>
+    <tableColumn id="6" xr3:uid="{9EB326C3-772E-4E56-89FB-BA3A00291293}" name="Autumn Week 3" dataDxfId="62"/>
+    <tableColumn id="7" xr3:uid="{94BC6C78-5A89-4267-B1C1-BFA70E5A9F34}" name="Autumn Week 4" dataDxfId="61"/>
+    <tableColumn id="8" xr3:uid="{CF3B6389-B559-4FE3-8B33-FEDB303382B1}" name="Autumn Week 5" dataDxfId="60"/>
+    <tableColumn id="9" xr3:uid="{8DD80B9C-D1B1-4CDE-A624-4CD3A15113DD}" name="Autumn Week 6" dataDxfId="59"/>
+    <tableColumn id="10" xr3:uid="{8C4EBEE4-01CB-4AD0-B594-F466CC36D370}" name="Autumn Week 7" dataDxfId="58"/>
+    <tableColumn id="11" xr3:uid="{7F8C91DE-BE61-47CF-A916-D06ED7B283E9}" name="Autumn Week 8" dataDxfId="57"/>
+    <tableColumn id="12" xr3:uid="{9D58139A-0F96-4203-8D22-58BC34744B87}" name="Autumn Week 9" dataDxfId="56"/>
+    <tableColumn id="13" xr3:uid="{43C545DF-9B9E-4080-8012-F9EFA0F01283}" name="Autumn Week 10" dataDxfId="55"/>
+    <tableColumn id="14" xr3:uid="{829AB976-2AB2-435C-8F11-DE08DACA4407}" name="Autumn Week 11" dataDxfId="54"/>
+    <tableColumn id="15" xr3:uid="{9126A0EA-FC34-4876-9D56-A0AC39C5526C}" name="Autumn Week 12" dataDxfId="53"/>
+    <tableColumn id="17" xr3:uid="{15B891EE-FCC8-4E53-A90D-3E10FFC1E9FA}" name="Spring Week 1" dataDxfId="52"/>
+    <tableColumn id="18" xr3:uid="{464CA212-3B53-4678-AFE4-8AF8308C1986}" name="Spring Week 2" dataDxfId="51"/>
+    <tableColumn id="19" xr3:uid="{B560E823-CC29-418C-B26C-52D9FFC8C72E}" name="Spring Week 3" dataDxfId="50"/>
+    <tableColumn id="20" xr3:uid="{D95606F3-E0A0-4907-91E0-4AD09D0C65CB}" name="Spring Week 4" dataDxfId="49"/>
+    <tableColumn id="21" xr3:uid="{E71FF892-9A4B-444C-8972-62D92F81B0E7}" name="Spring Week 5" dataDxfId="48"/>
+    <tableColumn id="22" xr3:uid="{C7775BA8-178A-4501-A8DE-2B2CF77A2451}" name="Spring Week 6" dataDxfId="47"/>
+    <tableColumn id="23" xr3:uid="{51A89A97-F839-4F50-88A9-65049D65C9B0}" name="Spring Week 7" dataDxfId="46"/>
+    <tableColumn id="24" xr3:uid="{26EE6D10-4FC4-49AE-8DE6-18AC556C293D}" name="Spring Week 8" dataDxfId="45"/>
+    <tableColumn id="25" xr3:uid="{FCB1B9FB-21DA-415A-86E6-C8E14F864E1B}" name="Spring Week 9" dataDxfId="44"/>
+    <tableColumn id="26" xr3:uid="{54402AE1-DC77-41BA-BCC7-28BCA7186B44}" name="Spring Week 10" dataDxfId="43"/>
+    <tableColumn id="27" xr3:uid="{31C092D1-BD77-4126-8E72-8E74D0D11509}" name="Spring Week 11" dataDxfId="42"/>
+    <tableColumn id="28" xr3:uid="{56D67770-E36A-46FE-97FA-76CD24229C51}" name="Spring Week 12" dataDxfId="41"/>
+    <tableColumn id="38" xr3:uid="{29E08DCE-0D92-40C5-8F33-F1B96FB2F7A4}" name="Spring Exams" dataDxfId="40"/>
+    <tableColumn id="29" xr3:uid="{785AD842-5ED0-4E27-B4B7-26E6FF9AC266}" name="Sub-total" dataDxfId="39">
       <calculatedColumnFormula>SUMIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0",Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="35" xr3:uid="{EE5D0E71-7823-4EE2-9CC1-32BF500AB742}" name="Total Hours" dataDxfId="74">
+    <tableColumn id="35" xr3:uid="{EE5D0E71-7823-4EE2-9CC1-32BF500AB742}" name="Total Hours" dataDxfId="38">
       <calculatedColumnFormula>IF(Table1[[#This Row],[Hours]]&gt;0,Table1[[#This Row],[Hours]],Table1[[#This Row],[Nominal Hours]])*COUNTIF(Table1[[#This Row],[Autumn Week 1]:[Spring Week 12]],"&gt;0")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9810,49 +9810,49 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A071F52D-AD51-4120-94C5-67D4117EBD07}" name="Table14" displayName="Table14" ref="A1:AE64" totalsRowShown="0" headerRowDxfId="73" dataDxfId="71" headerRowBorderDxfId="72" tableBorderDxfId="70" totalsRowBorderDxfId="69">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A071F52D-AD51-4120-94C5-67D4117EBD07}" name="Table14" displayName="Table14" ref="A1:AE64" totalsRowShown="0" headerRowDxfId="116" dataDxfId="114" headerRowBorderDxfId="115" tableBorderDxfId="113" totalsRowBorderDxfId="112">
   <autoFilter ref="A1:AE64" xr:uid="{FA69A777-C149-48BD-B248-35F32F0AC920}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AD64">
     <sortCondition ref="A1:A132"/>
   </sortState>
   <tableColumns count="31">
-    <tableColumn id="1" xr3:uid="{D7CE4D57-09F4-4B9D-B464-A087075D1C39}" name="Module Code" dataDxfId="68"/>
-    <tableColumn id="2" xr3:uid="{DE2920B2-70AC-48F3-99E7-07B70BC1E928}" name="Module Title" dataDxfId="67"/>
-    <tableColumn id="3" xr3:uid="{61946E7A-4C82-425B-89A6-3DBD530FCD55}" name="Contact type" dataDxfId="66"/>
-    <tableColumn id="34" xr3:uid="{55A68E2B-9324-4E9E-9629-6611EC7C904E}" name="Credits" dataDxfId="65">
+    <tableColumn id="1" xr3:uid="{D7CE4D57-09F4-4B9D-B464-A087075D1C39}" name="Module Code" dataDxfId="111"/>
+    <tableColumn id="2" xr3:uid="{DE2920B2-70AC-48F3-99E7-07B70BC1E928}" name="Module Title" dataDxfId="110"/>
+    <tableColumn id="3" xr3:uid="{61946E7A-4C82-425B-89A6-3DBD530FCD55}" name="Contact type" dataDxfId="109"/>
+    <tableColumn id="34" xr3:uid="{55A68E2B-9324-4E9E-9629-6611EC7C904E}" name="Credits" dataDxfId="108">
       <calculatedColumnFormula>INDEX(Table2[Credits],MATCH(Table14[[#This Row],[Module Code]],Table2[Module Code],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="30" xr3:uid="{9C4C2C35-CE5A-4469-93FA-21FC6F57EDAD}" name="Semester" dataDxfId="64">
+    <tableColumn id="30" xr3:uid="{9C4C2C35-CE5A-4469-93FA-21FC6F57EDAD}" name="Semester" dataDxfId="107">
       <calculatedColumnFormula>INDEX(Table2[Semester],MATCH(Table14[[#This Row],[Module Code]],Table2[Module Code],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="31" xr3:uid="{A7B09E14-0C35-459D-A9D0-5143D8AFFE4E}" name="Nominal Hours" dataDxfId="63">
+    <tableColumn id="31" xr3:uid="{A7B09E14-0C35-459D-A9D0-5143D8AFFE4E}" name="Nominal Hours" dataDxfId="106">
       <calculatedColumnFormula>INDEX(Table2[Contact Time],MATCH(Table14[[#This Row],[Module Code]],Table2[Module Code],0))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{503822B3-8862-4FCD-9DD3-3B52F57A97BE}" name="Autumn Week 1" dataDxfId="62"/>
-    <tableColumn id="5" xr3:uid="{760391D0-3219-4B11-8E3D-3E00EEDFA9DD}" name="Autumn Week 2" dataDxfId="61"/>
-    <tableColumn id="6" xr3:uid="{6EE5E3E9-C4FB-49BE-932C-B84EA0A7970D}" name="Autumn Week 3" dataDxfId="60"/>
-    <tableColumn id="7" xr3:uid="{2C7AD515-480E-49A6-8076-95205ACF95EC}" name="Autumn Week 4" dataDxfId="59"/>
-    <tableColumn id="8" xr3:uid="{6FD8C5C6-433E-493B-BB28-5ADD15CFC7FB}" name="Autumn Week 5" dataDxfId="58"/>
-    <tableColumn id="9" xr3:uid="{801E6BE2-75F8-40A5-A263-0AAEFDAA63E7}" name="Autumn Week 6" dataDxfId="57"/>
-    <tableColumn id="10" xr3:uid="{976D463A-C6BC-4636-B732-53E6CDF3F6C7}" name="Autumn Week 7" dataDxfId="56"/>
-    <tableColumn id="11" xr3:uid="{D025F987-6302-4D7B-9A9A-636F867D1872}" name="Autumn Week 8" dataDxfId="55"/>
-    <tableColumn id="12" xr3:uid="{D30D10EE-2DE5-4659-AA67-2134D11D6119}" name="Autumn Week 9" dataDxfId="54"/>
-    <tableColumn id="13" xr3:uid="{35E8F713-2D13-47B7-9811-293DA89F0D62}" name="Autumn Week 10" dataDxfId="53"/>
-    <tableColumn id="14" xr3:uid="{5DD48606-F817-4B30-8BA1-A96457CBB489}" name="Autumn Week 11" dataDxfId="52"/>
-    <tableColumn id="15" xr3:uid="{9B982ED1-A4C5-4E87-99AB-70713F2B634E}" name="Autumn Week 12" dataDxfId="51"/>
-    <tableColumn id="17" xr3:uid="{3AFDFF11-D351-428A-AC16-E674EB9DD7CC}" name="Spring Week 1" dataDxfId="50"/>
-    <tableColumn id="18" xr3:uid="{1431E9F9-328E-4229-9377-39D94C660D67}" name="Spring Week 2" dataDxfId="49"/>
-    <tableColumn id="19" xr3:uid="{8E1051DB-2A93-4ABA-8317-8F9921CF483D}" name="Spring Week 3" dataDxfId="48"/>
-    <tableColumn id="20" xr3:uid="{98B745E4-C481-42FF-9D3B-0D0899BD3DB6}" name="Spring Week 4" dataDxfId="47"/>
-    <tableColumn id="21" xr3:uid="{2FC9B562-4622-444D-9372-5637BFE48E0A}" name="Spring Week 5" dataDxfId="46"/>
-    <tableColumn id="22" xr3:uid="{95778D77-82F1-4B00-8FED-6FEB2BF83C3D}" name="Spring Week 6" dataDxfId="45"/>
-    <tableColumn id="23" xr3:uid="{9A49A64C-9A09-47A0-BC65-A8C1C98DACA3}" name="Spring Week 7" dataDxfId="44"/>
-    <tableColumn id="24" xr3:uid="{191AACBA-3CF0-48E5-B522-FCD2CCE9AC99}" name="Spring Week 8" dataDxfId="43"/>
-    <tableColumn id="25" xr3:uid="{DC35B6C1-904B-4E6A-A04F-ADF850A50D85}" name="Spring Week 9" dataDxfId="42"/>
-    <tableColumn id="26" xr3:uid="{BEB9E86A-57BF-4A1E-A499-BADB9EAD1DE9}" name="Spring Week 10" dataDxfId="41"/>
-    <tableColumn id="27" xr3:uid="{D640FB81-F093-4E3F-B7A1-6995DDDD6305}" name="Spring Week 11" dataDxfId="40"/>
-    <tableColumn id="28" xr3:uid="{496FDC17-F0F2-4381-96DA-177DC578A786}" name="Spring Week 12" dataDxfId="39"/>
-    <tableColumn id="32" xr3:uid="{65BCC67A-5DC9-4957-BB42-BCF5FCA71B17}" name="Total" dataDxfId="38">
+    <tableColumn id="4" xr3:uid="{503822B3-8862-4FCD-9DD3-3B52F57A97BE}" name="Autumn Week 1" dataDxfId="105"/>
+    <tableColumn id="5" xr3:uid="{760391D0-3219-4B11-8E3D-3E00EEDFA9DD}" name="Autumn Week 2" dataDxfId="104"/>
+    <tableColumn id="6" xr3:uid="{6EE5E3E9-C4FB-49BE-932C-B84EA0A7970D}" name="Autumn Week 3" dataDxfId="103"/>
+    <tableColumn id="7" xr3:uid="{2C7AD515-480E-49A6-8076-95205ACF95EC}" name="Autumn Week 4" dataDxfId="102"/>
+    <tableColumn id="8" xr3:uid="{6FD8C5C6-433E-493B-BB28-5ADD15CFC7FB}" name="Autumn Week 5" dataDxfId="101"/>
+    <tableColumn id="9" xr3:uid="{801E6BE2-75F8-40A5-A263-0AAEFDAA63E7}" name="Autumn Week 6" dataDxfId="100"/>
+    <tableColumn id="10" xr3:uid="{976D463A-C6BC-4636-B732-53E6CDF3F6C7}" name="Autumn Week 7" dataDxfId="99"/>
+    <tableColumn id="11" xr3:uid="{D025F987-6302-4D7B-9A9A-636F867D1872}" name="Autumn Week 8" dataDxfId="98"/>
+    <tableColumn id="12" xr3:uid="{D30D10EE-2DE5-4659-AA67-2134D11D6119}" name="Autumn Week 9" dataDxfId="97"/>
+    <tableColumn id="13" xr3:uid="{35E8F713-2D13-47B7-9811-293DA89F0D62}" name="Autumn Week 10" dataDxfId="96"/>
+    <tableColumn id="14" xr3:uid="{5DD48606-F817-4B30-8BA1-A96457CBB489}" name="Autumn Week 11" dataDxfId="95"/>
+    <tableColumn id="15" xr3:uid="{9B982ED1-A4C5-4E87-99AB-70713F2B634E}" name="Autumn Week 12" dataDxfId="94"/>
+    <tableColumn id="17" xr3:uid="{3AFDFF11-D351-428A-AC16-E674EB9DD7CC}" name="Spring Week 1" dataDxfId="93"/>
+    <tableColumn id="18" xr3:uid="{1431E9F9-328E-4229-9377-39D94C660D67}" name="Spring Week 2" dataDxfId="92"/>
+    <tableColumn id="19" xr3:uid="{8E1051DB-2A93-4ABA-8317-8F9921CF483D}" name="Spring Week 3" dataDxfId="91"/>
+    <tableColumn id="20" xr3:uid="{98B745E4-C481-42FF-9D3B-0D0899BD3DB6}" name="Spring Week 4" dataDxfId="90"/>
+    <tableColumn id="21" xr3:uid="{2FC9B562-4622-444D-9372-5637BFE48E0A}" name="Spring Week 5" dataDxfId="89"/>
+    <tableColumn id="22" xr3:uid="{95778D77-82F1-4B00-8FED-6FEB2BF83C3D}" name="Spring Week 6" dataDxfId="88"/>
+    <tableColumn id="23" xr3:uid="{9A49A64C-9A09-47A0-BC65-A8C1C98DACA3}" name="Spring Week 7" dataDxfId="87"/>
+    <tableColumn id="24" xr3:uid="{191AACBA-3CF0-48E5-B522-FCD2CCE9AC99}" name="Spring Week 8" dataDxfId="86"/>
+    <tableColumn id="25" xr3:uid="{DC35B6C1-904B-4E6A-A04F-ADF850A50D85}" name="Spring Week 9" dataDxfId="85"/>
+    <tableColumn id="26" xr3:uid="{BEB9E86A-57BF-4A1E-A499-BADB9EAD1DE9}" name="Spring Week 10" dataDxfId="84"/>
+    <tableColumn id="27" xr3:uid="{D640FB81-F093-4E3F-B7A1-6995DDDD6305}" name="Spring Week 11" dataDxfId="83"/>
+    <tableColumn id="28" xr3:uid="{496FDC17-F0F2-4381-96DA-177DC578A786}" name="Spring Week 12" dataDxfId="82"/>
+    <tableColumn id="32" xr3:uid="{65BCC67A-5DC9-4957-BB42-BCF5FCA71B17}" name="Total" dataDxfId="81">
       <calculatedColumnFormula>SUM(Table14[[#This Row],[Autumn Week 1]:[Spring Week 12]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -12381,9 +12381,11 @@
       <c r="R27" s="18"/>
       <c r="S27" s="19"/>
       <c r="T27" s="18">
+        <v>-0.2</v>
+      </c>
+      <c r="U27" s="18">
         <v>0.2</v>
       </c>
-      <c r="U27" s="18"/>
       <c r="V27" s="18"/>
       <c r="W27" s="19"/>
       <c r="X27" s="20"/>
@@ -23320,11 +23322,9 @@
       <c r="L170" s="18"/>
       <c r="M170" s="18"/>
       <c r="N170" s="18"/>
-      <c r="O170" s="19">
+      <c r="O170" s="19"/>
+      <c r="P170" s="18">
         <v>0.3</v>
-      </c>
-      <c r="P170" s="18">
-        <v>-0.3</v>
       </c>
       <c r="Q170" s="18"/>
       <c r="R170" s="18"/>
